--- a/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C80CC3F1-3BE5-4117-AF70-8B30EB461AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BBA6FE1-624E-4447-8580-4E9EEC7703C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1203,18 +1203,192 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_SAU_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_SAU_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_SAU_031</t>
   </si>
   <si>
@@ -1227,6 +1401,84 @@
     <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
+    <t>distr_solelc_spv_SAU_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_SAU_016</t>
   </si>
   <si>
@@ -1251,40 +1503,40 @@
     <t>connecting solar to buses in cluster 57</t>
   </si>
   <si>
-    <t>distr_solelc_spv_SAU_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
+    <t>distr_solelc_spv_SAU_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
   </si>
   <si>
     <t>distr_solelc_spv_SAU_004</t>
@@ -1299,108 +1551,6 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_SAU_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_SAU_051</t>
   </si>
   <si>
@@ -1413,174 +1563,120 @@
     <t>connecting solar to buses in cluster 48</t>
   </si>
   <si>
-    <t>distr_solelc_spv_SAU_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w586137460-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w900157271-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w900157271-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_SA4-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU,e_w900157271-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w198144511-230_SAU</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w597093579-380_SAU,e_w198144511-230_SAU</t>
+  </si>
+  <si>
+    <t>e_w198144511-230_SAU,e_w900157271-380_SAU</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_w582073817-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w818080067-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w820233467-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU,e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w203627872-380_SAU,e_w115168488-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w586137460-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
     <t>e_w203627872-380_SAU,e_w115168488-380_SAU,e_w204824991-380_SAU</t>
   </si>
   <si>
     <t>e_w204824991-380_SAU,e_w586137460-380_SAU,e_w899264357-380_SAU</t>
   </si>
   <si>
-    <t>e_w586137460-380_SAU</t>
+    <t>e_SA4-380_SAU,e_w818080067-380_SAU</t>
   </si>
   <si>
     <t>e_w582073817-380_SAU,e_w818080067-380_SAU</t>
   </si>
   <si>
+    <t>e_w582073817-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w820233467-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_SA12-380_SAU,e_w1317464635-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_SA4-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
     <t>e_w115168488-380_SAU,e_w524688755-380_SAU,e_w524938770-380_SAU,e_w203627872-380_SAU,e_w1317464635-380_SAU</t>
   </si>
   <si>
@@ -1590,118 +1686,100 @@
     <t>e_w207785816-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
   </si>
   <si>
-    <t>e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w597093579-380_SAU,e_w198144511-230_SAU</t>
-  </si>
-  <si>
-    <t>e_w198144511-230_SAU,e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w900157271-380_SAU</t>
+    <t>e_SA12-380_SAU,e_SA4-380_SAU,e_w582073817-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_w899264357-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU</t>
   </si>
   <si>
     <t>e_w818155745-380_SAU,e_w524938770-380_SAU</t>
   </si>
   <si>
-    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w582073817-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w820233467-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>e_SA4-380_SAU,e_w818080067-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_SA4-380_SAU,e_w582073817-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_w899264357-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU,e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU,e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w203627872-380_SAU,e_w115168488-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w586137460-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_SA12-380_SAU,e_w1317464635-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_SA4-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w582073817-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w818080067-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w820233467-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_SA4-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w198144511-230_SAU</t>
+    <t>distr_wonelc_won_SAU_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_SAU_006</t>
@@ -1710,34 +1788,154 @@
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SAU_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
+    <t>distr_wonelc_won_SAU_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_SAU_056</t>
@@ -1764,40 +1962,46 @@
     <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SAU_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>distr_wonelc_won_SAU_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_SAU_024</t>
@@ -1812,132 +2016,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SAU_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_SAU_047</t>
   </si>
   <si>
@@ -1968,106 +2046,169 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SAU_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_SAU_022</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU,e_w203627872-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_049</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_019</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_038</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_013</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_004</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_009</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_028</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU,e_w524938770-380_SAU,e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_042</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_035</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_020</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_014</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU,e_w586137460-380_SAU</t>
   </si>
   <si>
     <t>elc_won_SAU_006</t>
   </si>
   <si>
-    <t>elc_won_SAU_028</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU,e_w524938770-380_SAU,e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_042</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_035</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_020</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_014</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU,e_w586137460-380_SAU</t>
+    <t>elc_won_SAU_045</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_057</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_054</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_017</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_029</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_050</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_055</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_010</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_027</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_023</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_044</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU,e_SA12-380_SAU,e_w582073817-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_030</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_w1317464635-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_026</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_032</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w203627872-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_025</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_031</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_040</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_011</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_012</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_052</t>
+  </si>
+  <si>
+    <t>e_SA4-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_016</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_033</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_034</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_048</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_021</t>
   </si>
   <si>
     <t>elc_won_SAU_056</t>
@@ -2085,28 +2226,37 @@
     <t>e_w207785816-380_SAU,e_w899264357-380_SAU</t>
   </si>
   <si>
-    <t>elc_won_SAU_052</t>
-  </si>
-  <si>
-    <t>e_SA4-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_016</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_033</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_034</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_048</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_021</t>
+    <t>elc_won_SAU_005</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_046</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_051</t>
+  </si>
+  <si>
+    <t>e_w582073817-380_SAU,e_w818080067-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_053</t>
+  </si>
+  <si>
+    <t>e_SA4-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_002</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_041</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w204824991-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_015</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w207785816-380_SAU,e_w900157271-380_SAU</t>
   </si>
   <si>
     <t>elc_won_SAU_024</t>
@@ -2115,96 +2265,6 @@
     <t>elc_won_SAU_008</t>
   </si>
   <si>
-    <t>elc_won_SAU_005</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_045</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_057</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_054</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_017</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_041</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w204824991-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_015</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w207785816-380_SAU,e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_022</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU,e_w203627872-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_046</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_051</t>
-  </si>
-  <si>
-    <t>e_w582073817-380_SAU,e_w818080067-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_053</t>
-  </si>
-  <si>
-    <t>e_SA4-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_002</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_027</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_023</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_049</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_019</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_038</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_013</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_004</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_003</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_009</t>
-  </si>
-  <si>
     <t>elc_won_SAU_047</t>
   </si>
   <si>
@@ -2223,64 +2283,16 @@
     <t>elc_won_SAU_001</t>
   </si>
   <si>
-    <t>elc_won_SAU_029</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_050</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_055</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_010</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_044</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU,e_SA12-380_SAU,e_w582073817-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_030</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w1317464635-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_026</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_032</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w203627872-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_025</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_031</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_040</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_011</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_012</t>
+    <t>distr_wofelc_wof_SAU_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wofelc_wof_SAU_006</t>
@@ -2289,34 +2301,70 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_SAU_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_SAU_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_SAU_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
+    <t>distr_wofelc_wof_SAU_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_SAU_009</t>
@@ -2325,112 +2373,64 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_SAU_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>elc_wof_SAU_011</t>
+  </si>
+  <si>
+    <t>e_w524688755-380_SAU,e_w524938770-380_SAU,e_w115168488-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_008</t>
   </si>
   <si>
     <t>elc_wof_SAU_006</t>
   </si>
   <si>
+    <t>elc_wof_SAU_005</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_004</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_015</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_014</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_010</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_002</t>
+  </si>
+  <si>
     <t>elc_wof_SAU_007</t>
   </si>
   <si>
     <t>e_w203627872-380_SAU</t>
   </si>
   <si>
-    <t>elc_wof_SAU_008</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_005</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_004</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_011</t>
-  </si>
-  <si>
-    <t>e_w524688755-380_SAU,e_w524938770-380_SAU,e_w115168488-380_SAU</t>
+    <t>elc_wof_SAU_012</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_013</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_001</t>
+  </si>
+  <si>
+    <t>e_w203627872-380_SAU,e_w820233467-380_SAU</t>
   </si>
   <si>
     <t>elc_wof_SAU_009</t>
   </si>
   <si>
     <t>e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_012</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_015</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_014</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_001</t>
-  </si>
-  <si>
-    <t>e_w203627872-380_SAU,e_w820233467-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_013</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_003</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_010</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_002</t>
   </si>
   <si>
     <t>e_won_SAU_001</t>
@@ -7690,7 +7690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65312EAB-3B2F-4922-A546-E987322184E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED095D32-905C-4976-9413-56DB39BDCDCA}">
   <dimension ref="B9:BD69"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7928,16 +7928,16 @@
         <v>358</v>
       </c>
       <c r="Y11" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="Z11" t="s">
         <v>480</v>
       </c>
       <c r="AA11">
-        <v>0.99696268975079438</v>
+        <v>0.99452867739052209</v>
       </c>
       <c r="AB11">
-        <v>55.684021235436248</v>
+        <v>100.30758117376212</v>
       </c>
       <c r="AD11" t="s">
         <v>357</v>
@@ -7967,13 +7967,13 @@
         <v>639</v>
       </c>
       <c r="AN11" t="s">
-        <v>513</v>
+        <v>640</v>
       </c>
       <c r="AO11">
-        <v>0.99452344599216957</v>
+        <v>0.99537388871055088</v>
       </c>
       <c r="AP11">
-        <v>100.40349014355834</v>
+        <v>84.812040306566487</v>
       </c>
       <c r="AR11" t="s">
         <v>357</v>
@@ -8003,13 +8003,13 @@
         <v>748</v>
       </c>
       <c r="BB11" t="s">
-        <v>524</v>
+        <v>749</v>
       </c>
       <c r="BC11">
-        <v>0.99373441995445844</v>
+        <v>0.99328660809426739</v>
       </c>
       <c r="BD11">
-        <v>114.8689675015946</v>
+        <v>123.07885160509801</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8074,16 +8074,16 @@
         <v>362</v>
       </c>
       <c r="Y12" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="Z12" t="s">
         <v>481</v>
       </c>
       <c r="AA12">
-        <v>0.99080281040153462</v>
+        <v>0.97179899661735147</v>
       </c>
       <c r="AB12">
-        <v>168.61514263853132</v>
+        <v>517.01839534855594</v>
       </c>
       <c r="AD12" t="s">
         <v>357</v>
@@ -8110,16 +8110,16 @@
         <v>527</v>
       </c>
       <c r="AM12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AN12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AO12">
-        <v>0.99613173616148998</v>
+        <v>0.99137249123357829</v>
       </c>
       <c r="AP12">
-        <v>70.918170372684429</v>
+        <v>158.17099405106532</v>
       </c>
       <c r="AR12" t="s">
         <v>357</v>
@@ -8146,16 +8146,16 @@
         <v>720</v>
       </c>
       <c r="BA12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BB12" t="s">
-        <v>750</v>
+        <v>679</v>
       </c>
       <c r="BC12">
-        <v>0.9946830183430353</v>
+        <v>0.99562471898701166</v>
       </c>
       <c r="BD12">
-        <v>97.477997044351895</v>
+        <v>80.213485238119745</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8220,16 +8220,16 @@
         <v>364</v>
       </c>
       <c r="Y13" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="Z13" t="s">
         <v>482</v>
       </c>
       <c r="AA13">
-        <v>0.99579622489302932</v>
+        <v>0.99618185830423567</v>
       </c>
       <c r="AB13">
-        <v>77.069210294461683</v>
+        <v>69.999264422346712</v>
       </c>
       <c r="AD13" t="s">
         <v>357</v>
@@ -8256,16 +8256,16 @@
         <v>529</v>
       </c>
       <c r="AM13" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AN13" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="AO13">
-        <v>0.99401348566274372</v>
+        <v>0.99599332454910006</v>
       </c>
       <c r="AP13">
-        <v>109.75276284969773</v>
+        <v>73.455716599831945</v>
       </c>
       <c r="AR13" t="s">
         <v>357</v>
@@ -8295,13 +8295,13 @@
         <v>751</v>
       </c>
       <c r="BB13" t="s">
-        <v>711</v>
+        <v>488</v>
       </c>
       <c r="BC13">
-        <v>0.99562471898701166</v>
+        <v>0.99373441995445844</v>
       </c>
       <c r="BD13">
-        <v>80.213485238119745</v>
+        <v>114.8689675015946</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8366,16 +8366,16 @@
         <v>366</v>
       </c>
       <c r="Y14" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="Z14" t="s">
         <v>483</v>
       </c>
       <c r="AA14">
-        <v>0.99569030823620586</v>
+        <v>0.99382012268801767</v>
       </c>
       <c r="AB14">
-        <v>79.011015669559924</v>
+        <v>113.29775071967697</v>
       </c>
       <c r="AD14" t="s">
         <v>357</v>
@@ -8402,16 +8402,16 @@
         <v>531</v>
       </c>
       <c r="AM14" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN14" t="s">
-        <v>514</v>
+        <v>645</v>
       </c>
       <c r="AO14">
-        <v>0.99719505862833968</v>
+        <v>0.9911615033183967</v>
       </c>
       <c r="AP14">
-        <v>51.423925147105876</v>
+        <v>162.03910582939466</v>
       </c>
       <c r="AR14" t="s">
         <v>357</v>
@@ -8441,7 +8441,7 @@
         <v>752</v>
       </c>
       <c r="BB14" t="s">
-        <v>524</v>
+        <v>488</v>
       </c>
       <c r="BC14">
         <v>0.99258556051399616</v>
@@ -8512,16 +8512,16 @@
         <v>368</v>
       </c>
       <c r="Y15" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
       <c r="Z15" t="s">
         <v>484</v>
       </c>
       <c r="AA15">
-        <v>0.99830838325253757</v>
+        <v>0.96824382590461799</v>
       </c>
       <c r="AB15">
-        <v>31.012973703478178</v>
+        <v>582.19652508200454</v>
       </c>
       <c r="AD15" t="s">
         <v>357</v>
@@ -8548,16 +8548,16 @@
         <v>533</v>
       </c>
       <c r="AM15" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AN15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AO15">
-        <v>0.99756968390712597</v>
+        <v>0.99250307717988995</v>
       </c>
       <c r="AP15">
-        <v>44.555795036023476</v>
+        <v>137.44358503535005</v>
       </c>
       <c r="AR15" t="s">
         <v>357</v>
@@ -8587,7 +8587,7 @@
         <v>753</v>
       </c>
       <c r="BB15" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="BC15">
         <v>0.99780067380087223</v>
@@ -8658,16 +8658,16 @@
         <v>370</v>
       </c>
       <c r="Y16" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="Z16" t="s">
         <v>485</v>
       </c>
       <c r="AA16">
-        <v>0.9986424466209517</v>
+        <v>0.99779659814441168</v>
       </c>
       <c r="AB16">
-        <v>24.888478615885646</v>
+        <v>40.39570068578638</v>
       </c>
       <c r="AD16" t="s">
         <v>357</v>
@@ -8694,16 +8694,16 @@
         <v>535</v>
       </c>
       <c r="AM16" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AN16" t="s">
-        <v>646</v>
+        <v>487</v>
       </c>
       <c r="AO16">
-        <v>0.98633514910840148</v>
+        <v>0.99762828135527759</v>
       </c>
       <c r="AP16">
-        <v>250.52226634597372</v>
+        <v>43.481508486578257</v>
       </c>
       <c r="AR16" t="s">
         <v>357</v>
@@ -8733,13 +8733,13 @@
         <v>754</v>
       </c>
       <c r="BB16" t="s">
-        <v>755</v>
+        <v>524</v>
       </c>
       <c r="BC16">
-        <v>0.99328660809426739</v>
+        <v>0.99471771596794578</v>
       </c>
       <c r="BD16">
-        <v>123.07885160509801</v>
+        <v>96.841873920993507</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8804,16 +8804,16 @@
         <v>372</v>
       </c>
       <c r="Y17" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="Z17" t="s">
         <v>486</v>
       </c>
       <c r="AA17">
-        <v>0.99822251696597952</v>
+        <v>0.99312004901307538</v>
       </c>
       <c r="AB17">
-        <v>32.587188957042969</v>
+        <v>126.13243476028477</v>
       </c>
       <c r="AD17" t="s">
         <v>357</v>
@@ -8840,16 +8840,16 @@
         <v>537</v>
       </c>
       <c r="AM17" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN17" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="AO17">
-        <v>0.99423795514228697</v>
+        <v>0.99814919244123224</v>
       </c>
       <c r="AP17">
-        <v>105.63748905807284</v>
+        <v>33.93147191074226</v>
       </c>
       <c r="AR17" t="s">
         <v>357</v>
@@ -8876,16 +8876,16 @@
         <v>730</v>
       </c>
       <c r="BA17" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="BB17" t="s">
-        <v>757</v>
+        <v>524</v>
       </c>
       <c r="BC17">
-        <v>0.99598286193459573</v>
+        <v>0.99714954069979167</v>
       </c>
       <c r="BD17">
-        <v>73.647531199077619</v>
+        <v>52.258420503819536</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8950,16 +8950,16 @@
         <v>374</v>
       </c>
       <c r="Y18" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="Z18" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="AA18">
-        <v>0.99639561719714309</v>
+        <v>0.99550817361522914</v>
       </c>
       <c r="AB18">
-        <v>66.080351385710131</v>
+        <v>82.350150387465703</v>
       </c>
       <c r="AD18" t="s">
         <v>357</v>
@@ -8986,16 +8986,16 @@
         <v>539</v>
       </c>
       <c r="AM18" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AN18" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="AO18">
-        <v>0.99425224693549752</v>
+        <v>0.97472259529205563</v>
       </c>
       <c r="AP18">
-        <v>105.37547284921166</v>
+        <v>463.41908631231416</v>
       </c>
       <c r="AR18" t="s">
         <v>357</v>
@@ -9022,16 +9022,16 @@
         <v>732</v>
       </c>
       <c r="BA18" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="BB18" t="s">
-        <v>656</v>
+        <v>757</v>
       </c>
       <c r="BC18">
-        <v>0.99622586247638467</v>
+        <v>0.99662267470695765</v>
       </c>
       <c r="BD18">
-        <v>69.192521266280892</v>
+        <v>61.917630372443448</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9096,16 +9096,16 @@
         <v>376</v>
       </c>
       <c r="Y19" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="Z19" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AA19">
-        <v>0.99478325736787054</v>
+        <v>0.99833662864108064</v>
       </c>
       <c r="AB19">
-        <v>95.640281589039844</v>
+        <v>30.495141580187816</v>
       </c>
       <c r="AD19" t="s">
         <v>357</v>
@@ -9132,16 +9132,16 @@
         <v>541</v>
       </c>
       <c r="AM19" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN19" t="s">
-        <v>500</v>
+        <v>651</v>
       </c>
       <c r="AO19">
-        <v>0.99380453235646471</v>
+        <v>0.99613173616148998</v>
       </c>
       <c r="AP19">
-        <v>113.5835734648128</v>
+        <v>70.918170372684429</v>
       </c>
       <c r="AR19" t="s">
         <v>357</v>
@@ -9168,16 +9168,16 @@
         <v>734</v>
       </c>
       <c r="BA19" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="BB19" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
       <c r="BC19">
-        <v>0.99471771596794578</v>
+        <v>0.99041409381468681</v>
       </c>
       <c r="BD19">
-        <v>96.841873920993507</v>
+        <v>175.741613397409</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9242,16 +9242,16 @@
         <v>378</v>
       </c>
       <c r="Y20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA20">
-        <v>0.99387730304786159</v>
+        <v>0.99718955137263765</v>
       </c>
       <c r="AB20">
-        <v>112.24944412253714</v>
+        <v>51.524891501643573</v>
       </c>
       <c r="AD20" t="s">
         <v>357</v>
@@ -9278,16 +9278,16 @@
         <v>543</v>
       </c>
       <c r="AM20" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AN20" t="s">
-        <v>651</v>
+        <v>503</v>
       </c>
       <c r="AO20">
-        <v>0.99454709507143513</v>
+        <v>0.99401348566274372</v>
       </c>
       <c r="AP20">
-        <v>99.969923690355856</v>
+        <v>109.75276284969773</v>
       </c>
       <c r="AR20" t="s">
         <v>357</v>
@@ -9314,16 +9314,16 @@
         <v>736</v>
       </c>
       <c r="BA20" t="s">
+        <v>759</v>
+      </c>
+      <c r="BB20" t="s">
         <v>760</v>
       </c>
-      <c r="BB20" t="s">
-        <v>492</v>
-      </c>
       <c r="BC20">
-        <v>0.99714954069979167</v>
+        <v>0.9946830183430353</v>
       </c>
       <c r="BD20">
-        <v>52.258420503819536</v>
+        <v>97.477997044351895</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9388,16 +9388,16 @@
         <v>380</v>
       </c>
       <c r="Y21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Z21" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AA21">
-        <v>0.9988713684914583</v>
+        <v>0.99392843937740749</v>
       </c>
       <c r="AB21">
-        <v>20.691577656598067</v>
+        <v>111.31194474752928</v>
       </c>
       <c r="AD21" t="s">
         <v>357</v>
@@ -9424,16 +9424,16 @@
         <v>545</v>
       </c>
       <c r="AM21" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AN21" t="s">
-        <v>653</v>
+        <v>515</v>
       </c>
       <c r="AO21">
-        <v>0.99397984942240614</v>
+        <v>0.99719505862833968</v>
       </c>
       <c r="AP21">
-        <v>110.36942725588814</v>
+        <v>51.423925147105876</v>
       </c>
       <c r="AR21" t="s">
         <v>357</v>
@@ -9463,13 +9463,13 @@
         <v>761</v>
       </c>
       <c r="BB21" t="s">
-        <v>762</v>
+        <v>690</v>
       </c>
       <c r="BC21">
-        <v>0.990347747379142</v>
+        <v>0.99622586247638467</v>
       </c>
       <c r="BD21">
-        <v>176.95796471572925</v>
+        <v>69.192521266280892</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9534,16 +9534,16 @@
         <v>382</v>
       </c>
       <c r="Y22" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="Z22" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="AA22">
-        <v>0.99452867739052209</v>
+        <v>0.99639561719714309</v>
       </c>
       <c r="AB22">
-        <v>100.30758117376212</v>
+        <v>66.080351385710131</v>
       </c>
       <c r="AD22" t="s">
         <v>357</v>
@@ -9573,13 +9573,13 @@
         <v>654</v>
       </c>
       <c r="AN22" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="AO22">
-        <v>0.99357578681487824</v>
+        <v>0.99756968390712597</v>
       </c>
       <c r="AP22">
-        <v>117.77724172723266</v>
+        <v>44.555795036023476</v>
       </c>
       <c r="AR22" t="s">
         <v>357</v>
@@ -9606,16 +9606,16 @@
         <v>740</v>
       </c>
       <c r="BA22" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="BB22" t="s">
-        <v>764</v>
+        <v>517</v>
       </c>
       <c r="BC22">
-        <v>0.99340481758705135</v>
+        <v>0.98823641334977108</v>
       </c>
       <c r="BD22">
-        <v>120.9116775707251</v>
+        <v>215.66575525419617</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9680,16 +9680,16 @@
         <v>384</v>
       </c>
       <c r="Y23" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="Z23" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AA23">
-        <v>0.97179899661735147</v>
+        <v>0.99478325736787054</v>
       </c>
       <c r="AB23">
-        <v>517.01839534855594</v>
+        <v>95.640281589039844</v>
       </c>
       <c r="AD23" t="s">
         <v>357</v>
@@ -9722,10 +9722,10 @@
         <v>656</v>
       </c>
       <c r="AO23">
-        <v>0.99839984958131633</v>
+        <v>0.98633514910840148</v>
       </c>
       <c r="AP23">
-        <v>29.33609100920102</v>
+        <v>250.52226634597372</v>
       </c>
       <c r="AR23" t="s">
         <v>357</v>
@@ -9752,16 +9752,16 @@
         <v>742</v>
       </c>
       <c r="BA23" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="BB23" t="s">
-        <v>485</v>
+        <v>757</v>
       </c>
       <c r="BC23">
-        <v>0.98823641334977108</v>
+        <v>0.99340481758705135</v>
       </c>
       <c r="BD23">
-        <v>215.66575525419617</v>
+        <v>120.9116775707251</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9826,16 +9826,16 @@
         <v>386</v>
       </c>
       <c r="Y24" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="Z24" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AA24">
-        <v>0.99747091457046144</v>
+        <v>0.99387730304786159</v>
       </c>
       <c r="AB24">
-        <v>46.366566208207523</v>
+        <v>112.24944412253714</v>
       </c>
       <c r="AD24" t="s">
         <v>357</v>
@@ -9865,13 +9865,13 @@
         <v>657</v>
       </c>
       <c r="AN24" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="AO24">
-        <v>0.99753480556870955</v>
+        <v>0.99452344599216957</v>
       </c>
       <c r="AP24">
-        <v>45.195231240324411</v>
+        <v>100.40349014355834</v>
       </c>
       <c r="AR24" t="s">
         <v>357</v>
@@ -9898,16 +9898,16 @@
         <v>744</v>
       </c>
       <c r="BA24" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="BB24" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BC24">
-        <v>0.99662267470695765</v>
+        <v>0.990347747379142</v>
       </c>
       <c r="BD24">
-        <v>61.917630372443448</v>
+        <v>176.95796471572925</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9972,16 +9972,16 @@
         <v>388</v>
       </c>
       <c r="Y25" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="Z25" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="AA25">
-        <v>0.99505083080645407</v>
+        <v>0.9988713684914583</v>
       </c>
       <c r="AB25">
-        <v>90.734768548341648</v>
+        <v>20.691577656598067</v>
       </c>
       <c r="AD25" t="s">
         <v>357</v>
@@ -10011,13 +10011,13 @@
         <v>658</v>
       </c>
       <c r="AN25" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="AO25">
-        <v>0.99574634109779614</v>
+        <v>0.99597196524055454</v>
       </c>
       <c r="AP25">
-        <v>77.983746540404425</v>
+        <v>73.847303923166677</v>
       </c>
       <c r="AR25" t="s">
         <v>357</v>
@@ -10044,16 +10044,16 @@
         <v>746</v>
       </c>
       <c r="BA25" t="s">
+        <v>766</v>
+      </c>
+      <c r="BB25" t="s">
         <v>767</v>
       </c>
-      <c r="BB25" t="s">
-        <v>485</v>
-      </c>
       <c r="BC25">
-        <v>0.99041409381468681</v>
+        <v>0.99598286193459573</v>
       </c>
       <c r="BD25">
-        <v>175.741613397409</v>
+        <v>73.647531199077619</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10118,16 +10118,16 @@
         <v>390</v>
       </c>
       <c r="Y26" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="Z26" t="s">
         <v>493</v>
       </c>
       <c r="AA26">
-        <v>0.99618185830423567</v>
+        <v>0.99249760008191157</v>
       </c>
       <c r="AB26">
-        <v>69.999264422346712</v>
+        <v>137.54399849828698</v>
       </c>
       <c r="AD26" t="s">
         <v>357</v>
@@ -10157,13 +10157,13 @@
         <v>659</v>
       </c>
       <c r="AN26" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="AO26">
-        <v>0.99552667642160975</v>
+        <v>0.99592841699385404</v>
       </c>
       <c r="AP26">
-        <v>82.010932270487288</v>
+        <v>74.645688446009217</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10228,16 +10228,16 @@
         <v>392</v>
       </c>
       <c r="Y27" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="Z27" t="s">
         <v>494</v>
       </c>
       <c r="AA27">
-        <v>0.99382012268801767</v>
+        <v>0.99659574043303112</v>
       </c>
       <c r="AB27">
-        <v>113.29775071967697</v>
+        <v>62.411425394430239</v>
       </c>
       <c r="AD27" t="s">
         <v>357</v>
@@ -10267,13 +10267,13 @@
         <v>660</v>
       </c>
       <c r="AN27" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="AO27">
-        <v>0.99509394394688344</v>
+        <v>0.99603503633032486</v>
       </c>
       <c r="AP27">
-        <v>89.944360973802588</v>
+        <v>72.691000610711512</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10338,16 +10338,16 @@
         <v>394</v>
       </c>
       <c r="Y28" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="Z28" t="s">
         <v>495</v>
       </c>
       <c r="AA28">
-        <v>0.96824382590461799</v>
+        <v>0.99619933711347464</v>
       </c>
       <c r="AB28">
-        <v>582.19652508200454</v>
+        <v>69.678819586298616</v>
       </c>
       <c r="AD28" t="s">
         <v>357</v>
@@ -10377,13 +10377,13 @@
         <v>661</v>
       </c>
       <c r="AN28" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="AO28">
-        <v>0.98558431541919211</v>
+        <v>0.98797149625219505</v>
       </c>
       <c r="AP28">
-        <v>264.28755064814555</v>
+        <v>220.5225687097583</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10448,16 +10448,16 @@
         <v>396</v>
       </c>
       <c r="Y29" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="Z29" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="AA29">
-        <v>0.99706391072645384</v>
+        <v>0.9936489084537441</v>
       </c>
       <c r="AB29">
-        <v>53.828303348345614</v>
+        <v>116.43667834802481</v>
       </c>
       <c r="AD29" t="s">
         <v>357</v>
@@ -10487,13 +10487,13 @@
         <v>662</v>
       </c>
       <c r="AN29" t="s">
-        <v>489</v>
+        <v>663</v>
       </c>
       <c r="AO29">
-        <v>0.99417168399542333</v>
+        <v>0.99413068845869101</v>
       </c>
       <c r="AP29">
-        <v>106.85246008390632</v>
+        <v>107.60404492399896</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10558,16 +10558,16 @@
         <v>398</v>
       </c>
       <c r="Y30" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="Z30" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="AA30">
-        <v>0.99602776752751798</v>
+        <v>0.99646788098520922</v>
       </c>
       <c r="AB30">
-        <v>72.824261995504671</v>
+        <v>64.755515271164327</v>
       </c>
       <c r="AD30" t="s">
         <v>357</v>
@@ -10594,16 +10594,16 @@
         <v>563</v>
       </c>
       <c r="AM30" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AN30" t="s">
-        <v>507</v>
+        <v>665</v>
       </c>
       <c r="AO30">
-        <v>0.99597196524055454</v>
+        <v>0.99516481318893724</v>
       </c>
       <c r="AP30">
-        <v>73.847303923166677</v>
+        <v>88.645091536150389</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10668,16 +10668,16 @@
         <v>400</v>
       </c>
       <c r="Y31" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="Z31" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="AA31">
-        <v>0.99602904965813843</v>
+        <v>0.98251354146747882</v>
       </c>
       <c r="AB31">
-        <v>72.800756267461594</v>
+        <v>320.58507309622223</v>
       </c>
       <c r="AD31" t="s">
         <v>357</v>
@@ -10704,16 +10704,16 @@
         <v>565</v>
       </c>
       <c r="AM31" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AN31" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="AO31">
-        <v>0.99592841699385404</v>
+        <v>0.99575042910849376</v>
       </c>
       <c r="AP31">
-        <v>74.645688446009217</v>
+        <v>77.908799677615178</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10778,16 +10778,16 @@
         <v>402</v>
       </c>
       <c r="Y32" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="Z32" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="AA32">
-        <v>0.99749200922554471</v>
+        <v>0.99790048553623178</v>
       </c>
       <c r="AB32">
-        <v>45.979830865013916</v>
+        <v>38.491098502418218</v>
       </c>
       <c r="AD32" t="s">
         <v>357</v>
@@ -10814,16 +10814,16 @@
         <v>567</v>
       </c>
       <c r="AM32" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AN32" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="AO32">
-        <v>0.99603503633032486</v>
+        <v>0.97228963156816262</v>
       </c>
       <c r="AP32">
-        <v>72.691000610711512</v>
+        <v>508.02342125035216</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10888,16 +10888,16 @@
         <v>404</v>
       </c>
       <c r="Y33" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="Z33" t="s">
         <v>498</v>
       </c>
       <c r="AA33">
-        <v>0.99640650307416712</v>
+        <v>0.99660921899151722</v>
       </c>
       <c r="AB33">
-        <v>65.880776973603034</v>
+        <v>62.164318488851343</v>
       </c>
       <c r="AD33" t="s">
         <v>357</v>
@@ -10924,16 +10924,16 @@
         <v>569</v>
       </c>
       <c r="AM33" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AN33" t="s">
-        <v>495</v>
+        <v>669</v>
       </c>
       <c r="AO33">
-        <v>0.98797149625219505</v>
+        <v>0.99869856811798607</v>
       </c>
       <c r="AP33">
-        <v>220.5225687097583</v>
+        <v>23.859584503589375</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10998,16 +10998,16 @@
         <v>406</v>
       </c>
       <c r="Y34" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="Z34" t="s">
         <v>499</v>
       </c>
       <c r="AA34">
-        <v>0.99464283064821435</v>
+        <v>0.99069501978739871</v>
       </c>
       <c r="AB34">
-        <v>98.214771449403088</v>
+        <v>170.59130389769052</v>
       </c>
       <c r="AD34" t="s">
         <v>357</v>
@@ -11034,16 +11034,16 @@
         <v>571</v>
       </c>
       <c r="AM34" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AN34" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AO34">
-        <v>0.99095642121575722</v>
+        <v>0.99571112389324046</v>
       </c>
       <c r="AP34">
-        <v>165.79894437778461</v>
+        <v>78.629395290591617</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11108,16 +11108,16 @@
         <v>408</v>
       </c>
       <c r="Y35" t="s">
-        <v>342</v>
+        <v>305</v>
       </c>
       <c r="Z35" t="s">
         <v>500</v>
       </c>
       <c r="AA35">
-        <v>0.98546614984935366</v>
+        <v>0.995726462869435</v>
       </c>
       <c r="AB35">
-        <v>266.45391942851705</v>
+        <v>78.348180727024172</v>
       </c>
       <c r="AD35" t="s">
         <v>357</v>
@@ -11144,16 +11144,16 @@
         <v>573</v>
       </c>
       <c r="AM35" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AN35" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AO35">
-        <v>0.97944419839266028</v>
+        <v>0.9954181092030232</v>
       </c>
       <c r="AP35">
-        <v>376.85636280122765</v>
+        <v>84.001331277908477</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11218,16 +11218,16 @@
         <v>410</v>
       </c>
       <c r="Y36" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Z36" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="AA36">
-        <v>0.97830467520421338</v>
+        <v>0.99619958478128956</v>
       </c>
       <c r="AB36">
-        <v>397.74762125608811</v>
+        <v>69.674279009690451</v>
       </c>
       <c r="AD36" t="s">
         <v>357</v>
@@ -11254,16 +11254,16 @@
         <v>575</v>
       </c>
       <c r="AM36" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AN36" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="AO36">
-        <v>0.99537388871055088</v>
+        <v>0.99528882296736398</v>
       </c>
       <c r="AP36">
-        <v>84.812040306566487</v>
+        <v>86.371578931660309</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11328,16 +11328,16 @@
         <v>412</v>
       </c>
       <c r="Y37" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="Z37" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA37">
-        <v>0.99355869656544038</v>
+        <v>0.99467344166593308</v>
       </c>
       <c r="AB37">
-        <v>118.09056296692671</v>
+        <v>97.65356945789361</v>
       </c>
       <c r="AD37" t="s">
         <v>357</v>
@@ -11364,16 +11364,16 @@
         <v>577</v>
       </c>
       <c r="AM37" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="AN37" t="s">
-        <v>487</v>
+        <v>677</v>
       </c>
       <c r="AO37">
-        <v>0.99434230684812941</v>
+        <v>0.99790105131742324</v>
       </c>
       <c r="AP37">
-        <v>103.72437445096114</v>
+        <v>38.480725847241352</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11438,16 +11438,16 @@
         <v>414</v>
       </c>
       <c r="Y38" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="Z38" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA38">
-        <v>0.99465554801301226</v>
+        <v>0.99453893150792905</v>
       </c>
       <c r="AB38">
-        <v>97.981619761441394</v>
+        <v>100.11958902130077</v>
       </c>
       <c r="AD38" t="s">
         <v>357</v>
@@ -11474,16 +11474,16 @@
         <v>579</v>
       </c>
       <c r="AM38" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="AN38" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="AO38">
-        <v>0.99568064166004167</v>
+        <v>0.99879513173533752</v>
       </c>
       <c r="AP38">
-        <v>79.188236232570304</v>
+        <v>22.089251518811956</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11548,16 +11548,16 @@
         <v>416</v>
       </c>
       <c r="Y39" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="Z39" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA39">
-        <v>0.99559588972333779</v>
+        <v>0.98831357341581272</v>
       </c>
       <c r="AB39">
-        <v>80.74202173880623</v>
+        <v>214.25115404343418</v>
       </c>
       <c r="AD39" t="s">
         <v>357</v>
@@ -11584,16 +11584,16 @@
         <v>581</v>
       </c>
       <c r="AM39" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AN39" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AO39">
-        <v>0.99461370887370582</v>
+        <v>0.99784614270606442</v>
       </c>
       <c r="AP39">
-        <v>98.74867064872727</v>
+        <v>39.487383722152785</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11658,16 +11658,16 @@
         <v>418</v>
       </c>
       <c r="Y40" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="Z40" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA40">
-        <v>0.99304688575783195</v>
+        <v>0.99696268975079438</v>
       </c>
       <c r="AB40">
-        <v>127.47376110641395</v>
+        <v>55.684021235436248</v>
       </c>
       <c r="AD40" t="s">
         <v>357</v>
@@ -11694,16 +11694,16 @@
         <v>583</v>
       </c>
       <c r="AM40" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="AN40" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="AO40">
-        <v>0.99733419165525339</v>
+        <v>0.99808758387752583</v>
       </c>
       <c r="AP40">
-        <v>48.873152987020767</v>
+        <v>35.060962245360315</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11768,16 +11768,16 @@
         <v>420</v>
       </c>
       <c r="Y41" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z41" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA41">
-        <v>0.99457914346098975</v>
+        <v>0.99080281040153462</v>
       </c>
       <c r="AB41">
-        <v>99.382369881854956</v>
+        <v>168.61514263853132</v>
       </c>
       <c r="AD41" t="s">
         <v>357</v>
@@ -11804,16 +11804,16 @@
         <v>585</v>
       </c>
       <c r="AM41" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="AN41" t="s">
-        <v>680</v>
+        <v>480</v>
       </c>
       <c r="AO41">
-        <v>0.99869856811798607</v>
+        <v>0.99435834940894341</v>
       </c>
       <c r="AP41">
-        <v>23.859584503589375</v>
+        <v>103.43026083603691</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11878,16 +11878,16 @@
         <v>422</v>
       </c>
       <c r="Y42" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="Z42" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="AA42">
-        <v>0.99071604796665225</v>
+        <v>0.99579622489302932</v>
       </c>
       <c r="AB42">
-        <v>170.20578727804204</v>
+        <v>77.069210294461683</v>
       </c>
       <c r="AD42" t="s">
         <v>357</v>
@@ -11914,16 +11914,16 @@
         <v>587</v>
       </c>
       <c r="AM42" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="AN42" t="s">
-        <v>682</v>
+        <v>484</v>
       </c>
       <c r="AO42">
-        <v>0.99571112389324046</v>
+        <v>0.96791285861067489</v>
       </c>
       <c r="AP42">
-        <v>78.629395290591617</v>
+        <v>588.26425880429485</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11988,16 +11988,16 @@
         <v>424</v>
       </c>
       <c r="Y43" t="s">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="Z43" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="AA43">
-        <v>0.98761355430624809</v>
+        <v>0.99464283064821435</v>
       </c>
       <c r="AB43">
-        <v>227.08483771878468</v>
+        <v>98.214771449403088</v>
       </c>
       <c r="AD43" t="s">
         <v>357</v>
@@ -12024,16 +12024,16 @@
         <v>589</v>
       </c>
       <c r="AM43" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN43" t="s">
-        <v>684</v>
+        <v>484</v>
       </c>
       <c r="AO43">
-        <v>0.99137249123357829</v>
+        <v>0.97537069175149649</v>
       </c>
       <c r="AP43">
-        <v>158.17099405106532</v>
+        <v>451.53731788923056</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12098,16 +12098,16 @@
         <v>426</v>
       </c>
       <c r="Y44" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Z44" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="AA44">
-        <v>0.97378904282165912</v>
+        <v>0.98546614984935366</v>
       </c>
       <c r="AB44">
-        <v>480.53421493624944</v>
+        <v>266.45391942851705</v>
       </c>
       <c r="AD44" t="s">
         <v>357</v>
@@ -12134,16 +12134,16 @@
         <v>591</v>
       </c>
       <c r="AM44" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AN44" t="s">
-        <v>510</v>
+        <v>687</v>
       </c>
       <c r="AO44">
-        <v>0.99599332454910006</v>
+        <v>0.99397984942240614</v>
       </c>
       <c r="AP44">
-        <v>73.455716599831945</v>
+        <v>110.36942725588814</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12208,16 +12208,16 @@
         <v>428</v>
       </c>
       <c r="Y45" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="Z45" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="AA45">
-        <v>0.995726462869435</v>
+        <v>0.97830467520421338</v>
       </c>
       <c r="AB45">
-        <v>78.348180727024172</v>
+        <v>397.74762125608811</v>
       </c>
       <c r="AD45" t="s">
         <v>357</v>
@@ -12244,16 +12244,16 @@
         <v>593</v>
       </c>
       <c r="AM45" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AN45" t="s">
-        <v>687</v>
+        <v>523</v>
       </c>
       <c r="AO45">
-        <v>0.9911615033183967</v>
+        <v>0.99357578681487824</v>
       </c>
       <c r="AP45">
-        <v>162.03910582939466</v>
+        <v>117.77724172723266</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12318,16 +12318,16 @@
         <v>430</v>
       </c>
       <c r="Y46" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="Z46" t="s">
         <v>508</v>
       </c>
       <c r="AA46">
-        <v>0.99619958478128956</v>
+        <v>0.99706391072645384</v>
       </c>
       <c r="AB46">
-        <v>69.674279009690451</v>
+        <v>53.828303348345614</v>
       </c>
       <c r="AD46" t="s">
         <v>357</v>
@@ -12354,16 +12354,16 @@
         <v>595</v>
       </c>
       <c r="AM46" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AN46" t="s">
-        <v>482</v>
+        <v>690</v>
       </c>
       <c r="AO46">
-        <v>0.99250307717988995</v>
+        <v>0.99839984958131633</v>
       </c>
       <c r="AP46">
-        <v>137.44358503535005</v>
+        <v>29.33609100920102</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12428,16 +12428,16 @@
         <v>432</v>
       </c>
       <c r="Y47" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="Z47" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="AA47">
-        <v>0.99467344166593308</v>
+        <v>0.99602776752751798</v>
       </c>
       <c r="AB47">
-        <v>97.65356945789361</v>
+        <v>72.824261995504671</v>
       </c>
       <c r="AD47" t="s">
         <v>357</v>
@@ -12464,16 +12464,16 @@
         <v>597</v>
       </c>
       <c r="AM47" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AN47" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="AO47">
-        <v>0.99762828135527759</v>
+        <v>0.99753480556870955</v>
       </c>
       <c r="AP47">
-        <v>43.481508486578257</v>
+        <v>45.195231240324411</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12538,16 +12538,16 @@
         <v>434</v>
       </c>
       <c r="Y48" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="Z48" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AA48">
-        <v>0.99453893150792905</v>
+        <v>0.99602904965813843</v>
       </c>
       <c r="AB48">
-        <v>100.11958902130077</v>
+        <v>72.800756267461594</v>
       </c>
       <c r="AD48" t="s">
         <v>357</v>
@@ -12574,16 +12574,16 @@
         <v>599</v>
       </c>
       <c r="AM48" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AN48" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="AO48">
-        <v>0.99814919244123224</v>
+        <v>0.99574634109779614</v>
       </c>
       <c r="AP48">
-        <v>33.93147191074226</v>
+        <v>77.983746540404425</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12648,16 +12648,16 @@
         <v>436</v>
       </c>
       <c r="Y49" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="Z49" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AA49">
-        <v>0.98831357341581272</v>
+        <v>0.99749200922554471</v>
       </c>
       <c r="AB49">
-        <v>214.25115404343418</v>
+        <v>45.979830865013916</v>
       </c>
       <c r="AD49" t="s">
         <v>357</v>
@@ -12684,16 +12684,16 @@
         <v>601</v>
       </c>
       <c r="AM49" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AN49" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="AO49">
-        <v>0.97472259529205563</v>
+        <v>0.99552667642160975</v>
       </c>
       <c r="AP49">
-        <v>463.41908631231416</v>
+        <v>82.010932270487288</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12758,16 +12758,16 @@
         <v>438</v>
       </c>
       <c r="Y50" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="Z50" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AA50">
-        <v>0.99698542937844492</v>
+        <v>0.99640650307416712</v>
       </c>
       <c r="AB50">
-        <v>55.267128061843799</v>
+        <v>65.880776973603034</v>
       </c>
       <c r="AD50" t="s">
         <v>357</v>
@@ -12794,16 +12794,16 @@
         <v>603</v>
       </c>
       <c r="AM50" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AN50" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="AO50">
-        <v>0.99714785329843036</v>
+        <v>0.99423795514228697</v>
       </c>
       <c r="AP50">
-        <v>52.289356195443141</v>
+        <v>105.63748905807284</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12868,16 +12868,16 @@
         <v>440</v>
       </c>
       <c r="Y51" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Z51" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="AA51">
-        <v>0.9934828000061533</v>
+        <v>0.99698542937844492</v>
       </c>
       <c r="AB51">
-        <v>119.4819998871902</v>
+        <v>55.267128061843799</v>
       </c>
       <c r="AD51" t="s">
         <v>357</v>
@@ -12904,16 +12904,16 @@
         <v>605</v>
       </c>
       <c r="AM51" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AN51" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="AO51">
-        <v>0.99216195917442584</v>
+        <v>0.99425224693549752</v>
       </c>
       <c r="AP51">
-        <v>143.69741513552631</v>
+        <v>105.37547284921166</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12978,16 +12978,16 @@
         <v>442</v>
       </c>
       <c r="Y52" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Z52" t="s">
         <v>512</v>
       </c>
       <c r="AA52">
-        <v>0.99321708163681277</v>
+        <v>0.9934828000061533</v>
       </c>
       <c r="AB52">
-        <v>124.35350332509935</v>
+        <v>119.4819998871902</v>
       </c>
       <c r="AD52" t="s">
         <v>357</v>
@@ -13014,16 +13014,16 @@
         <v>607</v>
       </c>
       <c r="AM52" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AN52" t="s">
-        <v>695</v>
+        <v>504</v>
       </c>
       <c r="AO52">
-        <v>0.99621578293196666</v>
+        <v>0.99380453235646471</v>
       </c>
       <c r="AP52">
-        <v>69.377312913945246</v>
+        <v>113.5835734648128</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13088,16 +13088,16 @@
         <v>444</v>
       </c>
       <c r="Y53" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="Z53" t="s">
         <v>513</v>
       </c>
       <c r="AA53">
-        <v>0.99453867174093369</v>
+        <v>0.99321708163681277</v>
       </c>
       <c r="AB53">
-        <v>100.12435141621516</v>
+        <v>124.35350332509935</v>
       </c>
       <c r="AD53" t="s">
         <v>357</v>
@@ -13124,16 +13124,16 @@
         <v>609</v>
       </c>
       <c r="AM53" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AN53" t="s">
-        <v>506</v>
+        <v>698</v>
       </c>
       <c r="AO53">
-        <v>0.99480941720067528</v>
+        <v>0.99454709507143513</v>
       </c>
       <c r="AP53">
-        <v>95.160684654286598</v>
+        <v>99.969923690355856</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13198,16 +13198,16 @@
         <v>446</v>
       </c>
       <c r="Y54" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="Z54" t="s">
         <v>514</v>
       </c>
       <c r="AA54">
-        <v>0.99779322861139563</v>
+        <v>0.99453867174093369</v>
       </c>
       <c r="AB54">
-        <v>40.457475457746959</v>
+        <v>100.12435141621516</v>
       </c>
       <c r="AD54" t="s">
         <v>357</v>
@@ -13234,16 +13234,16 @@
         <v>611</v>
       </c>
       <c r="AM54" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AN54" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO54">
-        <v>0.99835008026027783</v>
+        <v>0.99417168399542333</v>
       </c>
       <c r="AP54">
-        <v>30.24852856157413</v>
+        <v>106.85246008390632</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13308,16 +13308,16 @@
         <v>448</v>
       </c>
       <c r="Y55" t="s">
-        <v>298</v>
+        <v>354</v>
       </c>
       <c r="Z55" t="s">
         <v>515</v>
       </c>
       <c r="AA55">
-        <v>0.99660921899151722</v>
+        <v>0.99779322861139563</v>
       </c>
       <c r="AB55">
-        <v>62.164318488851343</v>
+        <v>40.457475457746959</v>
       </c>
       <c r="AD55" t="s">
         <v>357</v>
@@ -13344,16 +13344,16 @@
         <v>613</v>
       </c>
       <c r="AM55" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AN55" t="s">
-        <v>699</v>
+        <v>489</v>
       </c>
       <c r="AO55">
-        <v>0.99413068845869101</v>
+        <v>0.99434230684812941</v>
       </c>
       <c r="AP55">
-        <v>107.60404492399896</v>
+        <v>103.72437445096114</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -13418,16 +13418,16 @@
         <v>450</v>
       </c>
       <c r="Y56" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="Z56" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="AA56">
-        <v>0.99069501978739871</v>
+        <v>0.99569030823620586</v>
       </c>
       <c r="AB56">
-        <v>170.59130389769052</v>
+        <v>79.011015669559924</v>
       </c>
       <c r="AD56" t="s">
         <v>357</v>
@@ -13454,16 +13454,16 @@
         <v>615</v>
       </c>
       <c r="AM56" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN56" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AO56">
-        <v>0.99516481318893724</v>
+        <v>0.99568064166004167</v>
       </c>
       <c r="AP56">
-        <v>88.645091536150389</v>
+        <v>79.188236232570304</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -13528,16 +13528,16 @@
         <v>452</v>
       </c>
       <c r="Y57" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="Z57" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AA57">
-        <v>0.99249760008191157</v>
+        <v>0.99830838325253757</v>
       </c>
       <c r="AB57">
-        <v>137.54399849828698</v>
+        <v>31.012973703478178</v>
       </c>
       <c r="AD57" t="s">
         <v>357</v>
@@ -13564,16 +13564,16 @@
         <v>617</v>
       </c>
       <c r="AM57" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AN57" t="s">
-        <v>502</v>
+        <v>704</v>
       </c>
       <c r="AO57">
-        <v>0.99575042910849376</v>
+        <v>0.99461370887370582</v>
       </c>
       <c r="AP57">
-        <v>77.908799677615178</v>
+        <v>98.74867064872727</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -13638,16 +13638,16 @@
         <v>454</v>
       </c>
       <c r="Y58" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="Z58" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AA58">
-        <v>0.99659574043303112</v>
+        <v>0.9986424466209517</v>
       </c>
       <c r="AB58">
-        <v>62.411425394430239</v>
+        <v>24.888478615885646</v>
       </c>
       <c r="AD58" t="s">
         <v>357</v>
@@ -13674,16 +13674,16 @@
         <v>619</v>
       </c>
       <c r="AM58" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AN58" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="AO58">
-        <v>0.97228963156816262</v>
+        <v>0.99733419165525339</v>
       </c>
       <c r="AP58">
-        <v>508.02342125035216</v>
+        <v>48.873152987020767</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -13748,16 +13748,16 @@
         <v>456</v>
       </c>
       <c r="Y59" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="Z59" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AA59">
-        <v>0.99619933711347464</v>
+        <v>0.99822251696597952</v>
       </c>
       <c r="AB59">
-        <v>69.678819586298616</v>
+        <v>32.587188957042969</v>
       </c>
       <c r="AD59" t="s">
         <v>357</v>
@@ -13784,16 +13784,16 @@
         <v>621</v>
       </c>
       <c r="AM59" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AN59" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AO59">
-        <v>0.9954181092030232</v>
+        <v>0.99095642121575722</v>
       </c>
       <c r="AP59">
-        <v>84.001331277908477</v>
+        <v>165.79894437778461</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -13858,16 +13858,16 @@
         <v>458</v>
       </c>
       <c r="Y60" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="Z60" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AA60">
-        <v>0.9936489084537441</v>
+        <v>0.99355869656544038</v>
       </c>
       <c r="AB60">
-        <v>116.43667834802481</v>
+        <v>118.09056296692671</v>
       </c>
       <c r="AD60" t="s">
         <v>357</v>
@@ -13894,16 +13894,16 @@
         <v>623</v>
       </c>
       <c r="AM60" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AN60" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AO60">
-        <v>0.99528882296736398</v>
+        <v>0.97944419839266028</v>
       </c>
       <c r="AP60">
-        <v>86.371578931660309</v>
+        <v>376.85636280122765</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -13968,16 +13968,16 @@
         <v>460</v>
       </c>
       <c r="Y61" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Z61" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AA61">
-        <v>0.99646788098520922</v>
+        <v>0.99465554801301226</v>
       </c>
       <c r="AB61">
-        <v>64.755515271164327</v>
+        <v>97.981619761441394</v>
       </c>
       <c r="AD61" t="s">
         <v>357</v>
@@ -14004,16 +14004,16 @@
         <v>625</v>
       </c>
       <c r="AM61" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AN61" t="s">
-        <v>709</v>
+        <v>502</v>
       </c>
       <c r="AO61">
-        <v>0.99790105131742324</v>
+        <v>0.99509394394688344</v>
       </c>
       <c r="AP61">
-        <v>38.480725847241352</v>
+        <v>89.944360973802588</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14078,16 +14078,16 @@
         <v>462</v>
       </c>
       <c r="Y62" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="Z62" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="AA62">
-        <v>0.98251354146747882</v>
+        <v>0.99559588972333779</v>
       </c>
       <c r="AB62">
-        <v>320.58507309622223</v>
+        <v>80.74202173880623</v>
       </c>
       <c r="AD62" t="s">
         <v>357</v>
@@ -14114,16 +14114,16 @@
         <v>627</v>
       </c>
       <c r="AM62" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AN62" t="s">
-        <v>711</v>
+        <v>484</v>
       </c>
       <c r="AO62">
-        <v>0.99879513173533752</v>
+        <v>0.98558431541919211</v>
       </c>
       <c r="AP62">
-        <v>22.089251518811956</v>
+        <v>264.28755064814555</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14188,16 +14188,16 @@
         <v>464</v>
       </c>
       <c r="Y63" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="Z63" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="AA63">
-        <v>0.99790048553623178</v>
+        <v>0.99304688575783195</v>
       </c>
       <c r="AB63">
-        <v>38.491098502418218</v>
+        <v>127.47376110641395</v>
       </c>
       <c r="AD63" t="s">
         <v>357</v>
@@ -14227,13 +14227,13 @@
         <v>712</v>
       </c>
       <c r="AN63" t="s">
-        <v>713</v>
+        <v>508</v>
       </c>
       <c r="AO63">
-        <v>0.99784614270606442</v>
+        <v>0.99714785329843036</v>
       </c>
       <c r="AP63">
-        <v>39.487383722152785</v>
+        <v>52.289356195443141</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14298,16 +14298,16 @@
         <v>466</v>
       </c>
       <c r="Y64" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="Z64" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AA64">
-        <v>0.99779659814441168</v>
+        <v>0.99457914346098975</v>
       </c>
       <c r="AB64">
-        <v>40.39570068578638</v>
+        <v>99.382369881854956</v>
       </c>
       <c r="AD64" t="s">
         <v>357</v>
@@ -14334,16 +14334,16 @@
         <v>631</v>
       </c>
       <c r="AM64" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AN64" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="AO64">
-        <v>0.99808758387752583</v>
+        <v>0.99216195917442584</v>
       </c>
       <c r="AP64">
-        <v>35.060962245360315</v>
+        <v>143.69741513552631</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14408,16 +14408,16 @@
         <v>468</v>
       </c>
       <c r="Y65" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="Z65" t="s">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="AA65">
-        <v>0.99312004901307538</v>
+        <v>0.99071604796665225</v>
       </c>
       <c r="AB65">
-        <v>126.13243476028477</v>
+        <v>170.20578727804204</v>
       </c>
       <c r="AD65" t="s">
         <v>357</v>
@@ -14444,16 +14444,16 @@
         <v>633</v>
       </c>
       <c r="AM65" t="s">
+        <v>714</v>
+      </c>
+      <c r="AN65" t="s">
         <v>715</v>
       </c>
-      <c r="AN65" t="s">
-        <v>482</v>
-      </c>
       <c r="AO65">
-        <v>0.99435834940894341</v>
+        <v>0.99621578293196666</v>
       </c>
       <c r="AP65">
-        <v>103.43026083603691</v>
+        <v>69.377312913945246</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -14518,16 +14518,16 @@
         <v>470</v>
       </c>
       <c r="Y66" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="Z66" t="s">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="AA66">
-        <v>0.99550817361522914</v>
+        <v>0.99747091457046144</v>
       </c>
       <c r="AB66">
-        <v>82.350150387465703</v>
+        <v>46.366566208207523</v>
       </c>
       <c r="AD66" t="s">
         <v>357</v>
@@ -14557,13 +14557,13 @@
         <v>716</v>
       </c>
       <c r="AN66" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="AO66">
-        <v>0.96791285861067489</v>
+        <v>0.99480941720067528</v>
       </c>
       <c r="AP66">
-        <v>588.26425880429485</v>
+        <v>95.160684654286598</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -14628,16 +14628,16 @@
         <v>472</v>
       </c>
       <c r="Y67" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="Z67" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AA67">
-        <v>0.99833662864108064</v>
+        <v>0.99505083080645407</v>
       </c>
       <c r="AB67">
-        <v>30.495141580187816</v>
+        <v>90.734768548341648</v>
       </c>
       <c r="AD67" t="s">
         <v>357</v>
@@ -14667,13 +14667,13 @@
         <v>717</v>
       </c>
       <c r="AN67" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AO67">
-        <v>0.97537069175149649</v>
+        <v>0.99835008026027783</v>
       </c>
       <c r="AP67">
-        <v>451.53731788923056</v>
+        <v>30.24852856157413</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -14738,16 +14738,16 @@
         <v>474</v>
       </c>
       <c r="Y68" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="Z68" t="s">
-        <v>524</v>
+        <v>484</v>
       </c>
       <c r="AA68">
-        <v>0.99718955137263765</v>
+        <v>0.98761355430624809</v>
       </c>
       <c r="AB68">
-        <v>51.524891501643573</v>
+        <v>227.08483771878468</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -14812,16 +14812,16 @@
         <v>476</v>
       </c>
       <c r="Y69" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="Z69" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="AA69">
-        <v>0.99392843937740749</v>
+        <v>0.97378904282165912</v>
       </c>
       <c r="AB69">
-        <v>111.31194474752928</v>
+        <v>480.53421493624944</v>
       </c>
     </row>
   </sheetData>
@@ -14830,7 +14830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52590025-8669-4E64-8114-EDBA9F90BFC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBD4BA-E6D0-487F-A2D4-312288402F29}">
   <dimension ref="B9:Z67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14942,7 +14942,7 @@
         <v>768</v>
       </c>
       <c r="K11" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="L11">
         <v>40.876322228443982</v>
@@ -14975,7 +14975,7 @@
         <v>882</v>
       </c>
       <c r="X11" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="Y11">
         <v>28.390499999999999</v>
@@ -15010,7 +15010,7 @@
         <v>770</v>
       </c>
       <c r="K12" t="s">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="L12">
         <v>50.805488525795006</v>
@@ -15043,7 +15043,7 @@
         <v>884</v>
       </c>
       <c r="X12" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="Y12">
         <v>11.62425</v>
@@ -15078,7 +15078,7 @@
         <v>772</v>
       </c>
       <c r="K13" t="s">
-        <v>690</v>
+        <v>648</v>
       </c>
       <c r="L13">
         <v>45.019365428022141</v>
@@ -15111,7 +15111,7 @@
         <v>886</v>
       </c>
       <c r="X13" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="Y13">
         <v>21.47775</v>
@@ -15146,7 +15146,7 @@
         <v>774</v>
       </c>
       <c r="K14" t="s">
-        <v>689</v>
+        <v>647</v>
       </c>
       <c r="L14">
         <v>38.91400567873454</v>
@@ -15214,7 +15214,7 @@
         <v>776</v>
       </c>
       <c r="K15" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="L15">
         <v>37.911583109814686</v>
@@ -15282,7 +15282,7 @@
         <v>778</v>
       </c>
       <c r="K16" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="L16">
         <v>37.473370534574258</v>
@@ -15315,7 +15315,7 @@
         <v>892</v>
       </c>
       <c r="X16" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="Y16">
         <v>27.628499999999999</v>
@@ -15350,7 +15350,7 @@
         <v>780</v>
       </c>
       <c r="K17" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="L17">
         <v>41.688010174294369</v>
@@ -15383,7 +15383,7 @@
         <v>894</v>
       </c>
       <c r="X17" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="Y17">
         <v>27.764250000000001</v>
@@ -15418,7 +15418,7 @@
         <v>782</v>
       </c>
       <c r="K18" t="s">
-        <v>661</v>
+        <v>711</v>
       </c>
       <c r="L18">
         <v>75.015285518414572</v>
@@ -15451,7 +15451,7 @@
         <v>896</v>
       </c>
       <c r="X18" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="Y18">
         <v>31.658999999999999</v>
@@ -15486,7 +15486,7 @@
         <v>784</v>
       </c>
       <c r="K19" t="s">
-        <v>691</v>
+        <v>649</v>
       </c>
       <c r="L19">
         <v>45.444678890317704</v>
@@ -15519,7 +15519,7 @@
         <v>898</v>
       </c>
       <c r="X19" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="Y19">
         <v>16.41</v>
@@ -15554,7 +15554,7 @@
         <v>786</v>
       </c>
       <c r="K20" t="s">
-        <v>703</v>
+        <v>667</v>
       </c>
       <c r="L20">
         <v>56.298031950426989</v>
@@ -15587,7 +15587,7 @@
         <v>900</v>
       </c>
       <c r="X20" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="Y20">
         <v>15.04425</v>
@@ -15622,7 +15622,7 @@
         <v>788</v>
       </c>
       <c r="K21" t="s">
-        <v>716</v>
+        <v>684</v>
       </c>
       <c r="L21">
         <v>40.148082022530652</v>
@@ -15655,7 +15655,7 @@
         <v>902</v>
       </c>
       <c r="X21" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="Y21">
         <v>25.41075</v>
@@ -15690,7 +15690,7 @@
         <v>790</v>
       </c>
       <c r="K22" t="s">
-        <v>717</v>
+        <v>685</v>
       </c>
       <c r="L22">
         <v>46.794583431146464</v>
@@ -15723,7 +15723,7 @@
         <v>904</v>
       </c>
       <c r="X22" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="Y22">
         <v>25.449000000000002</v>
@@ -15758,7 +15758,7 @@
         <v>792</v>
       </c>
       <c r="K23" t="s">
-        <v>688</v>
+        <v>646</v>
       </c>
       <c r="L23">
         <v>43.287064660921345</v>
@@ -15826,7 +15826,7 @@
         <v>794</v>
       </c>
       <c r="K24" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="L24">
         <v>33.920069303175502</v>
@@ -15859,7 +15859,7 @@
         <v>908</v>
       </c>
       <c r="X24" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="Y24">
         <v>4.7872500000000002</v>
@@ -15894,7 +15894,7 @@
         <v>796</v>
       </c>
       <c r="K25" t="s">
-        <v>669</v>
+        <v>708</v>
       </c>
       <c r="L25">
         <v>55.947913269125685</v>
@@ -15927,7 +15927,7 @@
         <v>910</v>
       </c>
       <c r="X25" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="Y25">
         <v>32.130749999999999</v>
@@ -15962,7 +15962,7 @@
         <v>798</v>
       </c>
       <c r="K26" t="s">
-        <v>654</v>
+        <v>688</v>
       </c>
       <c r="L26">
         <v>43.00072765840126</v>
@@ -15997,7 +15997,7 @@
         <v>800</v>
       </c>
       <c r="K27" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="L27">
         <v>39.635478438315815</v>
@@ -16032,7 +16032,7 @@
         <v>802</v>
       </c>
       <c r="K28" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="L28">
         <v>49.855646687868791</v>
@@ -16067,7 +16067,7 @@
         <v>804</v>
       </c>
       <c r="K29" t="s">
-        <v>685</v>
+        <v>643</v>
       </c>
       <c r="L29">
         <v>18.30570704636682</v>
@@ -16102,7 +16102,7 @@
         <v>806</v>
       </c>
       <c r="K30" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="L30">
         <v>12.148679200397462</v>
@@ -16137,7 +16137,7 @@
         <v>808</v>
       </c>
       <c r="K31" t="s">
-        <v>659</v>
+        <v>693</v>
       </c>
       <c r="L31">
         <v>26.575075296659808</v>
@@ -16172,7 +16172,7 @@
         <v>810</v>
       </c>
       <c r="K32" t="s">
-        <v>671</v>
+        <v>639</v>
       </c>
       <c r="L32">
         <v>38.722847502033055</v>
@@ -16207,7 +16207,7 @@
         <v>812</v>
       </c>
       <c r="K33" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="L33">
         <v>11.567890620729482</v>
@@ -16242,7 +16242,7 @@
         <v>814</v>
       </c>
       <c r="K34" t="s">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="L34">
         <v>39.131536885301792</v>
@@ -16277,7 +16277,7 @@
         <v>816</v>
       </c>
       <c r="K35" t="s">
-        <v>712</v>
+        <v>680</v>
       </c>
       <c r="L35">
         <v>20.394740302735183</v>
@@ -16312,7 +16312,7 @@
         <v>818</v>
       </c>
       <c r="K36" t="s">
-        <v>708</v>
+        <v>676</v>
       </c>
       <c r="L36">
         <v>9.0406747404738947</v>
@@ -16347,7 +16347,7 @@
         <v>820</v>
       </c>
       <c r="K37" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="L37">
         <v>6.4322833829685422</v>
@@ -16382,7 +16382,7 @@
         <v>822</v>
       </c>
       <c r="K38" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="L38">
         <v>35.845061923353079</v>
@@ -16417,7 +16417,7 @@
         <v>824</v>
       </c>
       <c r="K39" t="s">
-        <v>698</v>
+        <v>662</v>
       </c>
       <c r="L39">
         <v>14.004652736039368</v>
@@ -16452,7 +16452,7 @@
         <v>826</v>
       </c>
       <c r="K40" t="s">
-        <v>706</v>
+        <v>674</v>
       </c>
       <c r="L40">
         <v>18.855237278322775</v>
@@ -16487,7 +16487,7 @@
         <v>828</v>
       </c>
       <c r="K41" t="s">
-        <v>714</v>
+        <v>682</v>
       </c>
       <c r="L41">
         <v>1.5223012124511435</v>
@@ -16522,7 +16522,7 @@
         <v>830</v>
       </c>
       <c r="K42" t="s">
-        <v>710</v>
+        <v>678</v>
       </c>
       <c r="L42">
         <v>8.769590617684651</v>
@@ -16557,7 +16557,7 @@
         <v>832</v>
       </c>
       <c r="K43" t="s">
-        <v>655</v>
+        <v>689</v>
       </c>
       <c r="L43">
         <v>12.224014376407929</v>
@@ -16592,7 +16592,7 @@
         <v>834</v>
       </c>
       <c r="K44" t="s">
-        <v>657</v>
+        <v>691</v>
       </c>
       <c r="L44">
         <v>7.8604281920366468</v>
@@ -16627,7 +16627,7 @@
         <v>836</v>
       </c>
       <c r="K45" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="L45">
         <v>57.93121461085844</v>
@@ -16662,7 +16662,7 @@
         <v>838</v>
       </c>
       <c r="K46" t="s">
-        <v>649</v>
+        <v>696</v>
       </c>
       <c r="L46">
         <v>29.866420567467728</v>
@@ -16697,7 +16697,7 @@
         <v>840</v>
       </c>
       <c r="K47" t="s">
-        <v>650</v>
+        <v>697</v>
       </c>
       <c r="L47">
         <v>18.251138666339184</v>
@@ -16732,7 +16732,7 @@
         <v>842</v>
       </c>
       <c r="K48" t="s">
-        <v>686</v>
+        <v>644</v>
       </c>
       <c r="L48">
         <v>41.990618471497193</v>
@@ -16767,7 +16767,7 @@
         <v>844</v>
       </c>
       <c r="K49" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="L49">
         <v>47.169721640545575</v>
@@ -16802,7 +16802,7 @@
         <v>846</v>
       </c>
       <c r="K50" t="s">
-        <v>715</v>
+        <v>683</v>
       </c>
       <c r="L50">
         <v>32.605660023080361</v>
@@ -16837,7 +16837,7 @@
         <v>848</v>
       </c>
       <c r="K51" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="L51">
         <v>90.299482586246782</v>
@@ -16872,7 +16872,7 @@
         <v>850</v>
       </c>
       <c r="K52" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="L52">
         <v>31.0700693659116</v>
@@ -16907,7 +16907,7 @@
         <v>852</v>
       </c>
       <c r="K53" t="s">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="L53">
         <v>50.190949831504739</v>
@@ -16942,7 +16942,7 @@
         <v>854</v>
       </c>
       <c r="K54" t="s">
-        <v>704</v>
+        <v>672</v>
       </c>
       <c r="L54">
         <v>40.782965241127428</v>
@@ -16977,7 +16977,7 @@
         <v>856</v>
       </c>
       <c r="K55" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="L55">
         <v>18.78620106480027</v>
@@ -17012,7 +17012,7 @@
         <v>858</v>
       </c>
       <c r="K56" t="s">
-        <v>673</v>
+        <v>700</v>
       </c>
       <c r="L56">
         <v>36.951713341225911</v>
@@ -17047,7 +17047,7 @@
         <v>860</v>
       </c>
       <c r="K57" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="L57">
         <v>38.681111469396185</v>
@@ -17082,7 +17082,7 @@
         <v>862</v>
       </c>
       <c r="K58" t="s">
-        <v>658</v>
+        <v>692</v>
       </c>
       <c r="L58">
         <v>40.509643950316452</v>
@@ -17117,7 +17117,7 @@
         <v>864</v>
       </c>
       <c r="K59" t="s">
-        <v>683</v>
+        <v>641</v>
       </c>
       <c r="L59">
         <v>51.325262704004658</v>
@@ -17152,7 +17152,7 @@
         <v>866</v>
       </c>
       <c r="K60" t="s">
-        <v>700</v>
+        <v>664</v>
       </c>
       <c r="L60">
         <v>47.319604251931622</v>
@@ -17187,7 +17187,7 @@
         <v>868</v>
       </c>
       <c r="K61" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="L61">
         <v>62.987880701562105</v>
@@ -17222,7 +17222,7 @@
         <v>870</v>
       </c>
       <c r="K62" t="s">
-        <v>652</v>
+        <v>686</v>
       </c>
       <c r="L62">
         <v>31.448844031219011</v>
@@ -17257,7 +17257,7 @@
         <v>872</v>
       </c>
       <c r="K63" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
       <c r="L63">
         <v>42.295461693466549</v>
@@ -17292,7 +17292,7 @@
         <v>874</v>
       </c>
       <c r="K64" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="L64">
         <v>36.453082158597873</v>
@@ -17327,7 +17327,7 @@
         <v>876</v>
       </c>
       <c r="K65" t="s">
-        <v>702</v>
+        <v>666</v>
       </c>
       <c r="L65">
         <v>35.791395793730615</v>
@@ -17362,7 +17362,7 @@
         <v>878</v>
       </c>
       <c r="K66" t="s">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="L66">
         <v>50.483450907118872</v>
@@ -17397,7 +17397,7 @@
         <v>880</v>
       </c>
       <c r="K67" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="L67">
         <v>34.486778648232125</v>
@@ -17412,7 +17412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19B8509-8FFB-4485-9ABF-A77C84A3D92C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBC734F-643E-4D49-A51C-C31EE70837C9}">
   <dimension ref="B9:S119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C2715AB-DF0C-487D-A7FB-5545F3212B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C905F505-9CCD-4574-B386-4D354C986D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1203,18 +1203,156 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_SAU_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_SAU_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_SAU_042</t>
   </si>
   <si>
@@ -1233,6 +1371,132 @@
     <t>connecting solar to buses in cluster 56</t>
   </si>
   <si>
+    <t>distr_solelc_spv_SAU_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_SAU_037</t>
   </si>
   <si>
@@ -1245,6 +1509,48 @@
     <t>connecting solar to buses in cluster 47</t>
   </si>
   <si>
+    <t>distr_solelc_spv_SAU_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_SAU_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_SAU_004</t>
   </si>
   <si>
@@ -1257,321 +1563,66 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_SAU_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_SAU_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w181132741-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_SA4-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU,e_w900157271-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w198144511-230_SAU</t>
+  </si>
+  <si>
+    <t>e_w900157271-380_SAU</t>
+  </si>
+  <si>
+    <t>e_SA4-380_SAU,e_w818080067-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w582073817-380_SAU,e_w818080067-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w524688755-380_SAU,e_w524938770-380_SAU,e_w203627872-380_SAU,e_w1317464635-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w820233467-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU</t>
+  </si>
+  <si>
     <t>e_SA12-380_SAU</t>
   </si>
   <si>
+    <t>e_w582073817-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w820233467-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU</t>
+  </si>
+  <si>
     <t>e_w115168488-380_SAU,e_w204824991-380_SAU</t>
   </si>
   <si>
@@ -1581,127 +1632,226 @@
     <t>e_w198144511-230_SAU,e_w900157271-380_SAU</t>
   </si>
   <si>
-    <t>e_w586137460-380_SAU</t>
+    <t>e_w115168488-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w203627872-380_SAU,e_w115168488-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w586137460-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU,e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w203627872-380_SAU,e_w115168488-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w586137460-380_SAU</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_SA4-380_SAU,e_w582073817-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_w899264357-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_SA12-380_SAU,e_w1317464635-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_SA4-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w181132741-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w207785816-380_SAU</t>
   </si>
   <si>
     <t>e_w586137460-380_SAU,e_w900157271-380_SAU</t>
   </si>
   <si>
+    <t>e_SA12-380_SAU,e_w582073817-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w818080067-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w820233467-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
+  </si>
+  <si>
     <t>e_w818155745-380_SAU,e_w524938770-380_SAU</t>
   </si>
   <si>
-    <t>e_w582073817-380_SAU,e_w818080067-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w203627872-380_SAU,e_w115168488-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w586137460-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU,e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_SA12-380_SAU,e_w1317464635-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_SA4-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w203627872-380_SAU,e_w115168488-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w586137460-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w524688755-380_SAU,e_w524938770-380_SAU,e_w203627872-380_SAU,e_w1317464635-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w820233467-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
-  </si>
-  <si>
-    <t>e_SA4-380_SAU,e_w818080067-380_SAU</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_SA4-380_SAU,e_w582073817-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_w899264357-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU,e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w582073817-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w820233467-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w181132741-380_SAU,e_SA4-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w198144511-230_SAU</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w582073817-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w818080067-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w820233467-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w900157271-380_SAU,e_w198144511-230_SAU</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w899264357-380_SAU</t>
+    <t>distr_wonelc_won_SAU_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_SAU_052</t>
@@ -1716,76 +1866,130 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SAU_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>distr_wonelc_won_SAU_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_SAU_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_SAU_044</t>
@@ -1842,208 +2046,100 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_SAU_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_SAU_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_SAU_047</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_039</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_007</t>
+  </si>
+  <si>
+    <t>e_w899264357-380_SAU,e_w207785816-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_018</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_001</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_024</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_008</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_045</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_057</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_054</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_017</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_027</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_023</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_006</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_046</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_051</t>
+  </si>
+  <si>
+    <t>e_w582073817-380_SAU,e_w818080067-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_053</t>
+  </si>
+  <si>
+    <t>e_SA4-380_SAU,e_w597093579-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_002</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_049</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_019</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_038</t>
+  </si>
+  <si>
+    <t>e_w204824991-380_SAU,e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_013</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_004</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_009</t>
   </si>
   <si>
     <t>elc_won_SAU_052</t>
@@ -2055,49 +2151,94 @@
     <t>elc_won_SAU_016</t>
   </si>
   <si>
-    <t>elc_won_SAU_049</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_019</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_038</t>
-  </si>
-  <si>
-    <t>e_w204824991-380_SAU,e_w899264357-380_SAU,e_w586137460-380_SAU,e_w207785816-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_013</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_004</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_003</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_009</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_047</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_039</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_007</t>
-  </si>
-  <si>
-    <t>e_w899264357-380_SAU,e_w207785816-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_018</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_001</t>
+    <t>elc_won_SAU_033</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_034</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_048</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_021</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_056</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_043</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_036</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_037</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_028</t>
+  </si>
+  <si>
+    <t>e_w818155745-380_SAU,e_w524938770-380_SAU,e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_042</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_035</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_020</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_014</t>
+  </si>
+  <si>
+    <t>e_w207785816-380_SAU,e_w586137460-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_005</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_029</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU,e_SA12-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_050</t>
+  </si>
+  <si>
+    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_055</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_010</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_022</t>
+  </si>
+  <si>
+    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU,e_w203627872-380_SAU,e_w204824991-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_041</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w204824991-380_SAU,e_w899264357-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_won_SAU_015</t>
+  </si>
+  <si>
+    <t>e_w586137460-380_SAU,e_w207785816-380_SAU,e_w900157271-380_SAU</t>
   </si>
   <si>
     <t>elc_won_SAU_044</t>
@@ -2142,145 +2283,34 @@
     <t>elc_won_SAU_012</t>
   </si>
   <si>
-    <t>elc_won_SAU_024</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_008</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_028</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU,e_w524938770-380_SAU,e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_042</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_035</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_020</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_014</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU,e_w586137460-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_046</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_051</t>
-  </si>
-  <si>
-    <t>e_w582073817-380_SAU,e_w818080067-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_053</t>
-  </si>
-  <si>
-    <t>e_SA4-380_SAU,e_w597093579-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_002</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_006</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_056</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_043</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_036</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_037</t>
-  </si>
-  <si>
-    <t>e_w207785816-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_033</t>
-  </si>
-  <si>
-    <t>e_w818155745-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_034</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_048</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_021</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_022</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU,e_w203627872-380_SAU,e_w204824991-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_027</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_023</t>
-  </si>
-  <si>
-    <t>e_w1317464635-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_005</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_045</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_057</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_054</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_017</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_041</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w1317464635-380_SAU,e_w181132741-380_SAU,e_w204824991-380_SAU,e_w899264357-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_015</t>
-  </si>
-  <si>
-    <t>e_w586137460-380_SAU,e_w207785816-380_SAU,e_w900157271-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_029</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU,e_SA12-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_050</t>
-  </si>
-  <si>
-    <t>e_SA12-380_SAU,e_w582073817-380_SAU,e_SA4-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_055</t>
-  </si>
-  <si>
-    <t>elc_won_SAU_010</t>
+    <t>distr_wofelc_wof_SAU_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_SAU_001</t>
@@ -2295,6 +2325,18 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_SAU_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_SAU_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_SAU_015</t>
   </si>
   <si>
@@ -2307,22 +2349,10 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_SAU_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>distr_wofelc_wof_SAU_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wofelc_wof_SAU_006</t>
@@ -2331,24 +2361,6 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_SAU_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_SAU_005</t>
   </si>
   <si>
@@ -2361,16 +2373,25 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_SAU_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_SAU_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
+    <t>elc_wof_SAU_010</t>
+  </si>
+  <si>
+    <t>e_w524938770-380_SAU</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_002</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_008</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_003</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_009</t>
+  </si>
+  <si>
+    <t>e_w115168488-380_SAU,e_w524688755-380_SAU</t>
   </si>
   <si>
     <t>elc_wof_SAU_001</t>
@@ -2385,52 +2406,31 @@
     <t>e_w203627872-380_SAU</t>
   </si>
   <si>
+    <t>elc_wof_SAU_012</t>
+  </si>
+  <si>
+    <t>elc_wof_SAU_013</t>
+  </si>
+  <si>
     <t>elc_wof_SAU_015</t>
   </si>
   <si>
     <t>elc_wof_SAU_014</t>
   </si>
   <si>
-    <t>elc_wof_SAU_012</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_008</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_003</t>
+    <t>elc_wof_SAU_011</t>
+  </si>
+  <si>
+    <t>e_w524688755-380_SAU,e_w524938770-380_SAU,e_w115168488-380_SAU</t>
   </si>
   <si>
     <t>elc_wof_SAU_006</t>
   </si>
   <si>
-    <t>elc_wof_SAU_009</t>
-  </si>
-  <si>
-    <t>e_w115168488-380_SAU,e_w524688755-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_010</t>
-  </si>
-  <si>
-    <t>e_w524938770-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_002</t>
-  </si>
-  <si>
     <t>elc_wof_SAU_005</t>
   </si>
   <si>
     <t>elc_wof_SAU_004</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_011</t>
-  </si>
-  <si>
-    <t>e_w524688755-380_SAU,e_w524938770-380_SAU,e_w115168488-380_SAU</t>
-  </si>
-  <si>
-    <t>elc_wof_SAU_013</t>
   </si>
   <si>
     <t>e_won_SAU_001</t>
@@ -7699,7 +7699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2BD59F-78A8-4FA0-ADA1-758CB990D929}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352AD33E-CEA1-43E8-A3C8-4D89C7E72943}">
   <dimension ref="B9:BD69"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7937,16 +7937,16 @@
         <v>358</v>
       </c>
       <c r="Y11" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="Z11" t="s">
         <v>480</v>
       </c>
       <c r="AA11">
-        <v>0.99639561719714309</v>
+        <v>0.99779659814441168</v>
       </c>
       <c r="AB11">
-        <v>66.080351385710131</v>
+        <v>40.39570068578638</v>
       </c>
       <c r="AD11" t="s">
         <v>357</v>
@@ -7976,13 +7976,13 @@
         <v>639</v>
       </c>
       <c r="AN11" t="s">
-        <v>640</v>
+        <v>488</v>
       </c>
       <c r="AO11">
-        <v>0.99397984942240614</v>
+        <v>0.99714785329843036</v>
       </c>
       <c r="AP11">
-        <v>110.36942725588814</v>
+        <v>52.289356195443141</v>
       </c>
       <c r="AR11" t="s">
         <v>357</v>
@@ -8015,10 +8015,10 @@
         <v>749</v>
       </c>
       <c r="BC11">
-        <v>0.990347747379142</v>
+        <v>0.99662267470695765</v>
       </c>
       <c r="BD11">
-        <v>176.95796471572925</v>
+        <v>61.917630372443448</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8083,16 +8083,16 @@
         <v>362</v>
       </c>
       <c r="Y12" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="Z12" t="s">
         <v>481</v>
       </c>
       <c r="AA12">
-        <v>0.99478325736787054</v>
+        <v>0.99312004901307538</v>
       </c>
       <c r="AB12">
-        <v>95.640281589039844</v>
+        <v>126.13243476028477</v>
       </c>
       <c r="AD12" t="s">
         <v>357</v>
@@ -8119,16 +8119,16 @@
         <v>527</v>
       </c>
       <c r="AM12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AN12" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="AO12">
-        <v>0.99357578681487824</v>
+        <v>0.99216195917442584</v>
       </c>
       <c r="AP12">
-        <v>117.77724172723266</v>
+        <v>143.69741513552631</v>
       </c>
       <c r="AR12" t="s">
         <v>357</v>
@@ -8158,13 +8158,13 @@
         <v>750</v>
       </c>
       <c r="BB12" t="s">
-        <v>751</v>
+        <v>490</v>
       </c>
       <c r="BC12">
-        <v>0.9946830183430353</v>
+        <v>0.99041409381468681</v>
       </c>
       <c r="BD12">
-        <v>97.477997044351895</v>
+        <v>175.741613397409</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8229,16 +8229,16 @@
         <v>364</v>
       </c>
       <c r="Y13" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="Z13" t="s">
         <v>482</v>
       </c>
       <c r="AA13">
-        <v>0.99387730304786159</v>
+        <v>0.99550817361522914</v>
       </c>
       <c r="AB13">
-        <v>112.24944412253714</v>
+        <v>82.350150387465703</v>
       </c>
       <c r="AD13" t="s">
         <v>357</v>
@@ -8265,16 +8265,16 @@
         <v>529</v>
       </c>
       <c r="AM13" t="s">
+        <v>641</v>
+      </c>
+      <c r="AN13" t="s">
         <v>642</v>
       </c>
-      <c r="AN13" t="s">
-        <v>643</v>
-      </c>
       <c r="AO13">
-        <v>0.99137249123357829</v>
+        <v>0.99621578293196666</v>
       </c>
       <c r="AP13">
-        <v>158.17099405106532</v>
+        <v>69.377312913945246</v>
       </c>
       <c r="AR13" t="s">
         <v>357</v>
@@ -8301,16 +8301,16 @@
         <v>722</v>
       </c>
       <c r="BA13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="BB13" t="s">
-        <v>486</v>
+        <v>711</v>
       </c>
       <c r="BC13">
-        <v>0.99471771596794578</v>
+        <v>0.99562471898701166</v>
       </c>
       <c r="BD13">
-        <v>96.841873920993507</v>
+        <v>80.213485238119745</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8375,16 +8375,16 @@
         <v>366</v>
       </c>
       <c r="Y14" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Z14" t="s">
         <v>483</v>
       </c>
       <c r="AA14">
-        <v>0.9988713684914583</v>
+        <v>0.99833662864108064</v>
       </c>
       <c r="AB14">
-        <v>20.691577656598067</v>
+        <v>30.495141580187816</v>
       </c>
       <c r="AD14" t="s">
         <v>357</v>
@@ -8411,16 +8411,16 @@
         <v>531</v>
       </c>
       <c r="AM14" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AN14" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="AO14">
-        <v>0.99599332454910006</v>
+        <v>0.99480941720067528</v>
       </c>
       <c r="AP14">
-        <v>73.455716599831945</v>
+        <v>95.160684654286598</v>
       </c>
       <c r="AR14" t="s">
         <v>357</v>
@@ -8447,16 +8447,16 @@
         <v>724</v>
       </c>
       <c r="BA14" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="BB14" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="BC14">
-        <v>0.99714954069979167</v>
+        <v>0.98823641334977108</v>
       </c>
       <c r="BD14">
-        <v>52.258420503819536</v>
+        <v>215.66575525419617</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8521,16 +8521,16 @@
         <v>368</v>
       </c>
       <c r="Y15" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="Z15" t="s">
         <v>484</v>
       </c>
       <c r="AA15">
-        <v>0.99452867739052209</v>
+        <v>0.99718955137263765</v>
       </c>
       <c r="AB15">
-        <v>100.30758117376212</v>
+        <v>51.524891501643573</v>
       </c>
       <c r="AD15" t="s">
         <v>357</v>
@@ -8557,16 +8557,16 @@
         <v>533</v>
       </c>
       <c r="AM15" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AN15" t="s">
-        <v>646</v>
+        <v>500</v>
       </c>
       <c r="AO15">
-        <v>0.9911615033183967</v>
+        <v>0.99835008026027783</v>
       </c>
       <c r="AP15">
-        <v>162.03910582939466</v>
+        <v>30.24852856157413</v>
       </c>
       <c r="AR15" t="s">
         <v>357</v>
@@ -8593,16 +8593,16 @@
         <v>726</v>
       </c>
       <c r="BA15" t="s">
+        <v>753</v>
+      </c>
+      <c r="BB15" t="s">
         <v>754</v>
       </c>
-      <c r="BB15" t="s">
-        <v>693</v>
-      </c>
       <c r="BC15">
-        <v>0.99622586247638467</v>
+        <v>0.99598286193459573</v>
       </c>
       <c r="BD15">
-        <v>69.192521266280892</v>
+        <v>73.647531199077619</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8667,16 +8667,16 @@
         <v>370</v>
       </c>
       <c r="Y16" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="Z16" t="s">
         <v>485</v>
       </c>
       <c r="AA16">
-        <v>0.97179899661735147</v>
+        <v>0.99392843937740749</v>
       </c>
       <c r="AB16">
-        <v>517.01839534855594</v>
+        <v>111.31194474752928</v>
       </c>
       <c r="AD16" t="s">
         <v>357</v>
@@ -8703,16 +8703,16 @@
         <v>535</v>
       </c>
       <c r="AM16" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AN16" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="AO16">
-        <v>0.99250307717988995</v>
+        <v>0.99509394394688344</v>
       </c>
       <c r="AP16">
-        <v>137.44358503535005</v>
+        <v>89.944360973802588</v>
       </c>
       <c r="AR16" t="s">
         <v>357</v>
@@ -8742,13 +8742,13 @@
         <v>755</v>
       </c>
       <c r="BB16" t="s">
-        <v>664</v>
+        <v>756</v>
       </c>
       <c r="BC16">
-        <v>0.99562471898701166</v>
+        <v>0.990347747379142</v>
       </c>
       <c r="BD16">
-        <v>80.213485238119745</v>
+        <v>176.95796471572925</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8813,16 +8813,16 @@
         <v>372</v>
       </c>
       <c r="Y17" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="Z17" t="s">
         <v>486</v>
       </c>
       <c r="AA17">
-        <v>0.99747091457046144</v>
+        <v>0.99464283064821435</v>
       </c>
       <c r="AB17">
-        <v>46.366566208207523</v>
+        <v>98.214771449403088</v>
       </c>
       <c r="AD17" t="s">
         <v>357</v>
@@ -8849,16 +8849,16 @@
         <v>537</v>
       </c>
       <c r="AM17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AN17" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="AO17">
-        <v>0.99762828135527759</v>
+        <v>0.98558431541919211</v>
       </c>
       <c r="AP17">
-        <v>43.481508486578257</v>
+        <v>264.28755064814555</v>
       </c>
       <c r="AR17" t="s">
         <v>357</v>
@@ -8885,16 +8885,16 @@
         <v>730</v>
       </c>
       <c r="BA17" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BB17" t="s">
-        <v>503</v>
+        <v>758</v>
       </c>
       <c r="BC17">
-        <v>0.98823641334977108</v>
+        <v>0.9946830183430353</v>
       </c>
       <c r="BD17">
-        <v>215.66575525419617</v>
+        <v>97.477997044351895</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8959,16 +8959,16 @@
         <v>374</v>
       </c>
       <c r="Y18" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="Z18" t="s">
         <v>487</v>
       </c>
       <c r="AA18">
-        <v>0.99505083080645407</v>
+        <v>0.98546614984935366</v>
       </c>
       <c r="AB18">
-        <v>90.734768548341648</v>
+        <v>266.45391942851705</v>
       </c>
       <c r="AD18" t="s">
         <v>357</v>
@@ -8995,16 +8995,16 @@
         <v>539</v>
       </c>
       <c r="AM18" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AN18" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO18">
-        <v>0.99814919244123224</v>
+        <v>0.99597196524055454</v>
       </c>
       <c r="AP18">
-        <v>33.93147191074226</v>
+        <v>73.847303923166677</v>
       </c>
       <c r="AR18" t="s">
         <v>357</v>
@@ -9031,16 +9031,16 @@
         <v>732</v>
       </c>
       <c r="BA18" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="BB18" t="s">
-        <v>517</v>
+        <v>675</v>
       </c>
       <c r="BC18">
-        <v>0.99373441995445844</v>
+        <v>0.99622586247638467</v>
       </c>
       <c r="BD18">
-        <v>114.8689675015946</v>
+        <v>69.192521266280892</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9105,16 +9105,16 @@
         <v>376</v>
       </c>
       <c r="Y19" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="Z19" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AA19">
-        <v>0.99696268975079438</v>
+        <v>0.97830467520421338</v>
       </c>
       <c r="AB19">
-        <v>55.684021235436248</v>
+        <v>397.74762125608811</v>
       </c>
       <c r="AD19" t="s">
         <v>357</v>
@@ -9141,16 +9141,16 @@
         <v>541</v>
       </c>
       <c r="AM19" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AN19" t="s">
         <v>497</v>
       </c>
       <c r="AO19">
-        <v>0.97472259529205563</v>
+        <v>0.99592841699385404</v>
       </c>
       <c r="AP19">
-        <v>463.41908631231416</v>
+        <v>74.645688446009217</v>
       </c>
       <c r="AR19" t="s">
         <v>357</v>
@@ -9177,16 +9177,16 @@
         <v>734</v>
       </c>
       <c r="BA19" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="BB19" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="BC19">
-        <v>0.99598286193459573</v>
+        <v>0.99340481758705135</v>
       </c>
       <c r="BD19">
-        <v>73.647531199077619</v>
+        <v>120.9116775707251</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9251,16 +9251,16 @@
         <v>378</v>
       </c>
       <c r="Y20" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="Z20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA20">
-        <v>0.99080281040153462</v>
+        <v>0.99569030823620586</v>
       </c>
       <c r="AB20">
-        <v>168.61514263853132</v>
+        <v>79.011015669559924</v>
       </c>
       <c r="AD20" t="s">
         <v>357</v>
@@ -9287,16 +9287,16 @@
         <v>543</v>
       </c>
       <c r="AM20" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AN20" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="AO20">
-        <v>0.99714785329843036</v>
+        <v>0.99603503633032486</v>
       </c>
       <c r="AP20">
-        <v>52.289356195443141</v>
+        <v>72.691000610711512</v>
       </c>
       <c r="AR20" t="s">
         <v>357</v>
@@ -9323,16 +9323,16 @@
         <v>736</v>
       </c>
       <c r="BA20" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BB20" t="s">
-        <v>761</v>
+        <v>524</v>
       </c>
       <c r="BC20">
-        <v>0.99662267470695765</v>
+        <v>0.99471771596794578</v>
       </c>
       <c r="BD20">
-        <v>61.917630372443448</v>
+        <v>96.841873920993507</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9397,16 +9397,16 @@
         <v>380</v>
       </c>
       <c r="Y21" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="Z21" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AA21">
-        <v>0.99579622489302932</v>
+        <v>0.99830838325253757</v>
       </c>
       <c r="AB21">
-        <v>77.069210294461683</v>
+        <v>31.012973703478178</v>
       </c>
       <c r="AD21" t="s">
         <v>357</v>
@@ -9433,16 +9433,16 @@
         <v>545</v>
       </c>
       <c r="AM21" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AN21" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO21">
-        <v>0.99216195917442584</v>
+        <v>0.98797149625219505</v>
       </c>
       <c r="AP21">
-        <v>143.69741513552631</v>
+        <v>220.5225687097583</v>
       </c>
       <c r="AR21" t="s">
         <v>357</v>
@@ -9472,13 +9472,13 @@
         <v>762</v>
       </c>
       <c r="BB21" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="BC21">
-        <v>0.99041409381468681</v>
+        <v>0.99714954069979167</v>
       </c>
       <c r="BD21">
-        <v>175.741613397409</v>
+        <v>52.258420503819536</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9543,16 +9543,16 @@
         <v>382</v>
       </c>
       <c r="Y22" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="Z22" t="s">
         <v>490</v>
       </c>
       <c r="AA22">
-        <v>0.99698542937844492</v>
+        <v>0.9986424466209517</v>
       </c>
       <c r="AB22">
-        <v>55.267128061843799</v>
+        <v>24.888478615885646</v>
       </c>
       <c r="AD22" t="s">
         <v>357</v>
@@ -9579,16 +9579,16 @@
         <v>547</v>
       </c>
       <c r="AM22" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AN22" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AO22">
-        <v>0.99621578293196666</v>
+        <v>0.99869856811798607</v>
       </c>
       <c r="AP22">
-        <v>69.377312913945246</v>
+        <v>23.859584503589375</v>
       </c>
       <c r="AR22" t="s">
         <v>357</v>
@@ -9618,13 +9618,13 @@
         <v>763</v>
       </c>
       <c r="BB22" t="s">
-        <v>517</v>
+        <v>764</v>
       </c>
       <c r="BC22">
-        <v>0.99258556051399616</v>
+        <v>0.99328660809426739</v>
       </c>
       <c r="BD22">
-        <v>135.93139057673795</v>
+        <v>123.07885160509801</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9689,16 +9689,16 @@
         <v>384</v>
       </c>
       <c r="Y23" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="Z23" t="s">
         <v>491</v>
       </c>
       <c r="AA23">
-        <v>0.9934828000061533</v>
+        <v>0.99822251696597952</v>
       </c>
       <c r="AB23">
-        <v>119.4819998871902</v>
+        <v>32.587188957042969</v>
       </c>
       <c r="AD23" t="s">
         <v>357</v>
@@ -9725,16 +9725,16 @@
         <v>549</v>
       </c>
       <c r="AM23" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AN23" t="s">
-        <v>511</v>
+        <v>654</v>
       </c>
       <c r="AO23">
-        <v>0.99480941720067528</v>
+        <v>0.99571112389324046</v>
       </c>
       <c r="AP23">
-        <v>95.160684654286598</v>
+        <v>78.629395290591617</v>
       </c>
       <c r="AR23" t="s">
         <v>357</v>
@@ -9761,16 +9761,16 @@
         <v>742</v>
       </c>
       <c r="BA23" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BB23" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="BC23">
-        <v>0.99780067380087223</v>
+        <v>0.99373441995445844</v>
       </c>
       <c r="BD23">
-        <v>40.320980317341572</v>
+        <v>114.8689675015946</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9835,16 +9835,16 @@
         <v>386</v>
       </c>
       <c r="Y24" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Z24" t="s">
         <v>492</v>
       </c>
       <c r="AA24">
-        <v>0.99321708163681277</v>
+        <v>0.99618185830423567</v>
       </c>
       <c r="AB24">
-        <v>124.35350332509935</v>
+        <v>69.999264422346712</v>
       </c>
       <c r="AD24" t="s">
         <v>357</v>
@@ -9871,16 +9871,16 @@
         <v>551</v>
       </c>
       <c r="AM24" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AN24" t="s">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="AO24">
-        <v>0.99835008026027783</v>
+        <v>0.99452344599216957</v>
       </c>
       <c r="AP24">
-        <v>30.24852856157413</v>
+        <v>100.40349014355834</v>
       </c>
       <c r="AR24" t="s">
         <v>357</v>
@@ -9907,16 +9907,16 @@
         <v>744</v>
       </c>
       <c r="BA24" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="BB24" t="s">
-        <v>766</v>
+        <v>484</v>
       </c>
       <c r="BC24">
-        <v>0.99328660809426739</v>
+        <v>0.99258556051399616</v>
       </c>
       <c r="BD24">
-        <v>123.07885160509801</v>
+        <v>135.93139057673795</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9981,16 +9981,16 @@
         <v>388</v>
       </c>
       <c r="Y25" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="Z25" t="s">
         <v>493</v>
       </c>
       <c r="AA25">
-        <v>0.99453867174093369</v>
+        <v>0.99382012268801767</v>
       </c>
       <c r="AB25">
-        <v>100.12435141621516</v>
+        <v>113.29775071967697</v>
       </c>
       <c r="AD25" t="s">
         <v>357</v>
@@ -10017,16 +10017,16 @@
         <v>553</v>
       </c>
       <c r="AM25" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AN25" t="s">
-        <v>658</v>
+        <v>494</v>
       </c>
       <c r="AO25">
-        <v>0.9954181092030232</v>
+        <v>0.99434230684812941</v>
       </c>
       <c r="AP25">
-        <v>84.001331277908477</v>
+        <v>103.72437445096114</v>
       </c>
       <c r="AR25" t="s">
         <v>357</v>
@@ -10056,13 +10056,13 @@
         <v>767</v>
       </c>
       <c r="BB25" t="s">
-        <v>761</v>
+        <v>485</v>
       </c>
       <c r="BC25">
-        <v>0.99340481758705135</v>
+        <v>0.99780067380087223</v>
       </c>
       <c r="BD25">
-        <v>120.9116775707251</v>
+        <v>40.320980317341572</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10127,16 +10127,16 @@
         <v>390</v>
       </c>
       <c r="Y26" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="Z26" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="AA26">
-        <v>0.99779322861139563</v>
+        <v>0.96824382590461799</v>
       </c>
       <c r="AB26">
-        <v>40.457475457746959</v>
+        <v>582.19652508200454</v>
       </c>
       <c r="AD26" t="s">
         <v>357</v>
@@ -10163,16 +10163,16 @@
         <v>555</v>
       </c>
       <c r="AM26" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="AN26" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AO26">
-        <v>0.99528882296736398</v>
+        <v>0.99568064166004167</v>
       </c>
       <c r="AP26">
-        <v>86.371578931660309</v>
+        <v>79.188236232570304</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10237,16 +10237,16 @@
         <v>392</v>
       </c>
       <c r="Y27" t="s">
-        <v>302</v>
+        <v>347</v>
       </c>
       <c r="Z27" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="AA27">
-        <v>0.99618185830423567</v>
+        <v>0.98761355430624809</v>
       </c>
       <c r="AB27">
-        <v>69.999264422346712</v>
+        <v>227.08483771878468</v>
       </c>
       <c r="AD27" t="s">
         <v>357</v>
@@ -10273,16 +10273,16 @@
         <v>557</v>
       </c>
       <c r="AM27" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AN27" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AO27">
-        <v>0.99790105131742324</v>
+        <v>0.99461370887370582</v>
       </c>
       <c r="AP27">
-        <v>38.480725847241352</v>
+        <v>98.74867064872727</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10347,16 +10347,16 @@
         <v>394</v>
       </c>
       <c r="Y28" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Z28" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="AA28">
-        <v>0.99382012268801767</v>
+        <v>0.97378904282165912</v>
       </c>
       <c r="AB28">
-        <v>113.29775071967697</v>
+        <v>480.53421493624944</v>
       </c>
       <c r="AD28" t="s">
         <v>357</v>
@@ -10383,16 +10383,16 @@
         <v>559</v>
       </c>
       <c r="AM28" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AN28" t="s">
-        <v>664</v>
+        <v>485</v>
       </c>
       <c r="AO28">
-        <v>0.99879513173533752</v>
+        <v>0.99733419165525339</v>
       </c>
       <c r="AP28">
-        <v>22.089251518811956</v>
+        <v>48.873152987020767</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10457,16 +10457,16 @@
         <v>396</v>
       </c>
       <c r="Y29" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="Z29" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="AA29">
-        <v>0.96824382590461799</v>
+        <v>0.99706391072645384</v>
       </c>
       <c r="AB29">
-        <v>582.19652508200454</v>
+        <v>53.828303348345614</v>
       </c>
       <c r="AD29" t="s">
         <v>357</v>
@@ -10493,16 +10493,16 @@
         <v>561</v>
       </c>
       <c r="AM29" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="AN29" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="AO29">
-        <v>0.99784614270606442</v>
+        <v>0.99137249123357829</v>
       </c>
       <c r="AP29">
-        <v>39.487383722152785</v>
+        <v>158.17099405106532</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10567,16 +10567,16 @@
         <v>398</v>
       </c>
       <c r="Y30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Z30" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AA30">
-        <v>0.995726462869435</v>
+        <v>0.99602776752751798</v>
       </c>
       <c r="AB30">
-        <v>78.348180727024172</v>
+        <v>72.824261995504671</v>
       </c>
       <c r="AD30" t="s">
         <v>357</v>
@@ -10603,16 +10603,16 @@
         <v>563</v>
       </c>
       <c r="AM30" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="AN30" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="AO30">
-        <v>0.99808758387752583</v>
+        <v>0.99599332454910006</v>
       </c>
       <c r="AP30">
-        <v>35.060962245360315</v>
+        <v>73.455716599831945</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10677,16 +10677,16 @@
         <v>400</v>
       </c>
       <c r="Y31" t="s">
-        <v>339</v>
+        <v>309</v>
       </c>
       <c r="Z31" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AA31">
-        <v>0.99619958478128956</v>
+        <v>0.99602904965813843</v>
       </c>
       <c r="AB31">
-        <v>69.674279009690451</v>
+        <v>72.800756267461594</v>
       </c>
       <c r="AD31" t="s">
         <v>357</v>
@@ -10713,16 +10713,16 @@
         <v>565</v>
       </c>
       <c r="AM31" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="AN31" t="s">
-        <v>484</v>
+        <v>666</v>
       </c>
       <c r="AO31">
-        <v>0.99435834940894341</v>
+        <v>0.9911615033183967</v>
       </c>
       <c r="AP31">
-        <v>103.43026083603691</v>
+        <v>162.03910582939466</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10787,16 +10787,16 @@
         <v>402</v>
       </c>
       <c r="Y32" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="Z32" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AA32">
-        <v>0.99467344166593308</v>
+        <v>0.99749200922554471</v>
       </c>
       <c r="AB32">
-        <v>97.65356945789361</v>
+        <v>45.979830865013916</v>
       </c>
       <c r="AD32" t="s">
         <v>357</v>
@@ -10823,16 +10823,16 @@
         <v>567</v>
       </c>
       <c r="AM32" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AN32" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="AO32">
-        <v>0.96791285861067489</v>
+        <v>0.99250307717988995</v>
       </c>
       <c r="AP32">
-        <v>588.26425880429485</v>
+        <v>137.44358503535005</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10897,16 +10897,16 @@
         <v>404</v>
       </c>
       <c r="Y33" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="Z33" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AA33">
-        <v>0.99453893150792905</v>
+        <v>0.99640650307416712</v>
       </c>
       <c r="AB33">
-        <v>100.11958902130077</v>
+        <v>65.880776973603034</v>
       </c>
       <c r="AD33" t="s">
         <v>357</v>
@@ -10933,16 +10933,16 @@
         <v>569</v>
       </c>
       <c r="AM33" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AN33" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="AO33">
-        <v>0.97537069175149649</v>
+        <v>0.99762828135527759</v>
       </c>
       <c r="AP33">
-        <v>451.53731788923056</v>
+        <v>43.481508486578257</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -11007,16 +11007,16 @@
         <v>406</v>
       </c>
       <c r="Y34" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="Z34" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="AA34">
-        <v>0.98831357341581272</v>
+        <v>0.99639561719714309</v>
       </c>
       <c r="AB34">
-        <v>214.25115404343418</v>
+        <v>66.080351385710131</v>
       </c>
       <c r="AD34" t="s">
         <v>357</v>
@@ -11043,16 +11043,16 @@
         <v>571</v>
       </c>
       <c r="AM34" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="AN34" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="AO34">
-        <v>0.99509394394688344</v>
+        <v>0.99814919244123224</v>
       </c>
       <c r="AP34">
-        <v>89.944360973802588</v>
+        <v>33.93147191074226</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11117,16 +11117,16 @@
         <v>408</v>
       </c>
       <c r="Y35" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="Z35" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="AA35">
-        <v>0.99569030823620586</v>
+        <v>0.99478325736787054</v>
       </c>
       <c r="AB35">
-        <v>79.011015669559924</v>
+        <v>95.640281589039844</v>
       </c>
       <c r="AD35" t="s">
         <v>357</v>
@@ -11153,16 +11153,16 @@
         <v>573</v>
       </c>
       <c r="AM35" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="AN35" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AO35">
-        <v>0.98558431541919211</v>
+        <v>0.97472259529205563</v>
       </c>
       <c r="AP35">
-        <v>264.28755064814555</v>
+        <v>463.41908631231416</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11227,16 +11227,16 @@
         <v>410</v>
       </c>
       <c r="Y36" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="Z36" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AA36">
-        <v>0.99830838325253757</v>
+        <v>0.99387730304786159</v>
       </c>
       <c r="AB36">
-        <v>31.012973703478178</v>
+        <v>112.24944412253714</v>
       </c>
       <c r="AD36" t="s">
         <v>357</v>
@@ -11263,16 +11263,16 @@
         <v>575</v>
       </c>
       <c r="AM36" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="AN36" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AO36">
-        <v>0.99613173616148998</v>
+        <v>0.99397984942240614</v>
       </c>
       <c r="AP36">
-        <v>70.918170372684429</v>
+        <v>110.36942725588814</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11337,16 +11337,16 @@
         <v>412</v>
       </c>
       <c r="Y37" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="Z37" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AA37">
-        <v>0.9986424466209517</v>
+        <v>0.9988713684914583</v>
       </c>
       <c r="AB37">
-        <v>24.888478615885646</v>
+        <v>20.691577656598067</v>
       </c>
       <c r="AD37" t="s">
         <v>357</v>
@@ -11373,16 +11373,16 @@
         <v>577</v>
       </c>
       <c r="AM37" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AN37" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="AO37">
-        <v>0.99401348566274372</v>
+        <v>0.99357578681487824</v>
       </c>
       <c r="AP37">
-        <v>109.75276284969773</v>
+        <v>117.77724172723266</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11447,16 +11447,16 @@
         <v>414</v>
       </c>
       <c r="Y38" t="s">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="Z38" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AA38">
-        <v>0.99822251696597952</v>
+        <v>0.99660921899151722</v>
       </c>
       <c r="AB38">
-        <v>32.587188957042969</v>
+        <v>62.164318488851343</v>
       </c>
       <c r="AD38" t="s">
         <v>357</v>
@@ -11483,16 +11483,16 @@
         <v>579</v>
       </c>
       <c r="AM38" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AN38" t="s">
-        <v>494</v>
+        <v>675</v>
       </c>
       <c r="AO38">
-        <v>0.99719505862833968</v>
+        <v>0.99839984958131633</v>
       </c>
       <c r="AP38">
-        <v>51.423925147105876</v>
+        <v>29.33609100920102</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11557,16 +11557,16 @@
         <v>416</v>
       </c>
       <c r="Y39" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="Z39" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AA39">
-        <v>0.99464283064821435</v>
+        <v>0.99069501978739871</v>
       </c>
       <c r="AB39">
-        <v>98.214771449403088</v>
+        <v>170.59130389769052</v>
       </c>
       <c r="AD39" t="s">
         <v>357</v>
@@ -11593,16 +11593,16 @@
         <v>581</v>
       </c>
       <c r="AM39" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AN39" t="s">
-        <v>484</v>
+        <v>524</v>
       </c>
       <c r="AO39">
-        <v>0.99756968390712597</v>
+        <v>0.99753480556870955</v>
       </c>
       <c r="AP39">
-        <v>44.555795036023476</v>
+        <v>45.195231240324411</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11667,16 +11667,16 @@
         <v>418</v>
       </c>
       <c r="Y40" t="s">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="Z40" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AA40">
-        <v>0.98546614984935366</v>
+        <v>0.99696268975079438</v>
       </c>
       <c r="AB40">
-        <v>266.45391942851705</v>
+        <v>55.684021235436248</v>
       </c>
       <c r="AD40" t="s">
         <v>357</v>
@@ -11703,16 +11703,16 @@
         <v>583</v>
       </c>
       <c r="AM40" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AN40" t="s">
-        <v>679</v>
+        <v>488</v>
       </c>
       <c r="AO40">
-        <v>0.98633514910840148</v>
+        <v>0.99574634109779614</v>
       </c>
       <c r="AP40">
-        <v>250.52226634597372</v>
+        <v>77.983746540404425</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11777,16 +11777,16 @@
         <v>420</v>
       </c>
       <c r="Y41" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="Z41" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="AA41">
-        <v>0.97830467520421338</v>
+        <v>0.99080281040153462</v>
       </c>
       <c r="AB41">
-        <v>397.74762125608811</v>
+        <v>168.61514263853132</v>
       </c>
       <c r="AD41" t="s">
         <v>357</v>
@@ -11813,16 +11813,16 @@
         <v>585</v>
       </c>
       <c r="AM41" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AN41" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="AO41">
-        <v>0.99434230684812941</v>
+        <v>0.99552667642160975</v>
       </c>
       <c r="AP41">
-        <v>103.72437445096114</v>
+        <v>82.010932270487288</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11887,16 +11887,16 @@
         <v>422</v>
       </c>
       <c r="Y42" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="Z42" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="AA42">
-        <v>0.99355869656544038</v>
+        <v>0.99579622489302932</v>
       </c>
       <c r="AB42">
-        <v>118.09056296692671</v>
+        <v>77.069210294461683</v>
       </c>
       <c r="AD42" t="s">
         <v>357</v>
@@ -11923,16 +11923,16 @@
         <v>587</v>
       </c>
       <c r="AM42" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AN42" t="s">
-        <v>682</v>
+        <v>507</v>
       </c>
       <c r="AO42">
-        <v>0.99568064166004167</v>
+        <v>0.99423795514228697</v>
       </c>
       <c r="AP42">
-        <v>79.188236232570304</v>
+        <v>105.63748905807284</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11997,16 +11997,16 @@
         <v>424</v>
       </c>
       <c r="Y43" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="Z43" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AA43">
-        <v>0.99465554801301226</v>
+        <v>0.995726462869435</v>
       </c>
       <c r="AB43">
-        <v>97.981619761441394</v>
+        <v>78.348180727024172</v>
       </c>
       <c r="AD43" t="s">
         <v>357</v>
@@ -12033,16 +12033,16 @@
         <v>589</v>
       </c>
       <c r="AM43" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AN43" t="s">
-        <v>684</v>
+        <v>508</v>
       </c>
       <c r="AO43">
-        <v>0.99461370887370582</v>
+        <v>0.99425224693549752</v>
       </c>
       <c r="AP43">
-        <v>98.74867064872727</v>
+        <v>105.37547284921166</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12107,16 +12107,16 @@
         <v>426</v>
       </c>
       <c r="Y44" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="Z44" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AA44">
-        <v>0.99559588972333779</v>
+        <v>0.99619958478128956</v>
       </c>
       <c r="AB44">
-        <v>80.74202173880623</v>
+        <v>69.674279009690451</v>
       </c>
       <c r="AD44" t="s">
         <v>357</v>
@@ -12143,16 +12143,16 @@
         <v>591</v>
       </c>
       <c r="AM44" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="AN44" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="AO44">
-        <v>0.99733419165525339</v>
+        <v>0.99380453235646471</v>
       </c>
       <c r="AP44">
-        <v>48.873152987020767</v>
+        <v>113.5835734648128</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12217,16 +12217,16 @@
         <v>428</v>
       </c>
       <c r="Y45" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="Z45" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AA45">
-        <v>0.99304688575783195</v>
+        <v>0.99467344166593308</v>
       </c>
       <c r="AB45">
-        <v>127.47376110641395</v>
+        <v>97.65356945789361</v>
       </c>
       <c r="AD45" t="s">
         <v>357</v>
@@ -12253,16 +12253,16 @@
         <v>593</v>
       </c>
       <c r="AM45" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="AN45" t="s">
-        <v>493</v>
+        <v>683</v>
       </c>
       <c r="AO45">
-        <v>0.99452344599216957</v>
+        <v>0.99454709507143513</v>
       </c>
       <c r="AP45">
-        <v>100.40349014355834</v>
+        <v>99.969923690355856</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12327,16 +12327,16 @@
         <v>430</v>
       </c>
       <c r="Y46" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Z46" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AA46">
-        <v>0.99457914346098975</v>
+        <v>0.99453893150792905</v>
       </c>
       <c r="AB46">
-        <v>99.382369881854956</v>
+        <v>100.11958902130077</v>
       </c>
       <c r="AD46" t="s">
         <v>357</v>
@@ -12363,16 +12363,16 @@
         <v>595</v>
       </c>
       <c r="AM46" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AN46" t="s">
-        <v>499</v>
+        <v>685</v>
       </c>
       <c r="AO46">
-        <v>0.99423795514228697</v>
+        <v>0.99613173616148998</v>
       </c>
       <c r="AP46">
-        <v>105.63748905807284</v>
+        <v>70.918170372684429</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12437,16 +12437,16 @@
         <v>432</v>
       </c>
       <c r="Y47" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="Z47" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="AA47">
-        <v>0.99071604796665225</v>
+        <v>0.98831357341581272</v>
       </c>
       <c r="AB47">
-        <v>170.20578727804204</v>
+        <v>214.25115404343418</v>
       </c>
       <c r="AD47" t="s">
         <v>357</v>
@@ -12473,16 +12473,16 @@
         <v>597</v>
       </c>
       <c r="AM47" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="AN47" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="AO47">
-        <v>0.99425224693549752</v>
+        <v>0.99401348566274372</v>
       </c>
       <c r="AP47">
-        <v>105.37547284921166</v>
+        <v>109.75276284969773</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12547,16 +12547,16 @@
         <v>434</v>
       </c>
       <c r="Y48" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="Z48" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="AA48">
-        <v>0.99706391072645384</v>
+        <v>0.99355869656544038</v>
       </c>
       <c r="AB48">
-        <v>53.828303348345614</v>
+        <v>118.09056296692671</v>
       </c>
       <c r="AD48" t="s">
         <v>357</v>
@@ -12583,16 +12583,16 @@
         <v>599</v>
       </c>
       <c r="AM48" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AN48" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="AO48">
-        <v>0.99380453235646471</v>
+        <v>0.99719505862833968</v>
       </c>
       <c r="AP48">
-        <v>113.5835734648128</v>
+        <v>51.423925147105876</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12657,16 +12657,16 @@
         <v>436</v>
       </c>
       <c r="Y49" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="Z49" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="AA49">
-        <v>0.99602776752751798</v>
+        <v>0.99465554801301226</v>
       </c>
       <c r="AB49">
-        <v>72.824261995504671</v>
+        <v>97.981619761441394</v>
       </c>
       <c r="AD49" t="s">
         <v>357</v>
@@ -12693,16 +12693,16 @@
         <v>601</v>
       </c>
       <c r="AM49" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AN49" t="s">
-        <v>691</v>
+        <v>482</v>
       </c>
       <c r="AO49">
-        <v>0.99454709507143513</v>
+        <v>0.99756968390712597</v>
       </c>
       <c r="AP49">
-        <v>99.969923690355856</v>
+        <v>44.555795036023476</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12767,16 +12767,16 @@
         <v>438</v>
       </c>
       <c r="Y50" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="Z50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA50">
-        <v>0.99602904965813843</v>
+        <v>0.99559588972333779</v>
       </c>
       <c r="AB50">
-        <v>72.800756267461594</v>
+        <v>80.74202173880623</v>
       </c>
       <c r="AD50" t="s">
         <v>357</v>
@@ -12803,16 +12803,16 @@
         <v>603</v>
       </c>
       <c r="AM50" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AN50" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="AO50">
-        <v>0.99839984958131633</v>
+        <v>0.98633514910840148</v>
       </c>
       <c r="AP50">
-        <v>29.33609100920102</v>
+        <v>250.52226634597372</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12877,16 +12877,16 @@
         <v>440</v>
       </c>
       <c r="Y51" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="Z51" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AA51">
-        <v>0.99749200922554471</v>
+        <v>0.99304688575783195</v>
       </c>
       <c r="AB51">
-        <v>45.979830865013916</v>
+        <v>127.47376110641395</v>
       </c>
       <c r="AD51" t="s">
         <v>357</v>
@@ -12913,16 +12913,16 @@
         <v>605</v>
       </c>
       <c r="AM51" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="AN51" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="AO51">
-        <v>0.99753480556870955</v>
+        <v>0.99417168399542333</v>
       </c>
       <c r="AP51">
-        <v>45.195231240324411</v>
+        <v>106.85246008390632</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12987,16 +12987,16 @@
         <v>442</v>
       </c>
       <c r="Y52" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AA52">
-        <v>0.99640650307416712</v>
+        <v>0.99457914346098975</v>
       </c>
       <c r="AB52">
-        <v>65.880776973603034</v>
+        <v>99.382369881854956</v>
       </c>
       <c r="AD52" t="s">
         <v>357</v>
@@ -13023,16 +13023,16 @@
         <v>607</v>
       </c>
       <c r="AM52" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="AN52" t="s">
-        <v>487</v>
+        <v>693</v>
       </c>
       <c r="AO52">
-        <v>0.99574634109779614</v>
+        <v>0.99413068845869101</v>
       </c>
       <c r="AP52">
-        <v>77.983746540404425</v>
+        <v>107.60404492399896</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13097,16 +13097,16 @@
         <v>444</v>
       </c>
       <c r="Y53" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="Z53" t="s">
-        <v>515</v>
+        <v>483</v>
       </c>
       <c r="AA53">
-        <v>0.99779659814441168</v>
+        <v>0.99071604796665225</v>
       </c>
       <c r="AB53">
-        <v>40.39570068578638</v>
+        <v>170.20578727804204</v>
       </c>
       <c r="AD53" t="s">
         <v>357</v>
@@ -13133,16 +13133,16 @@
         <v>609</v>
       </c>
       <c r="AM53" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="AN53" t="s">
-        <v>481</v>
+        <v>695</v>
       </c>
       <c r="AO53">
-        <v>0.99552667642160975</v>
+        <v>0.99516481318893724</v>
       </c>
       <c r="AP53">
-        <v>82.010932270487288</v>
+        <v>88.645091536150389</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13207,16 +13207,16 @@
         <v>446</v>
       </c>
       <c r="Y54" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="Z54" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="AA54">
-        <v>0.99312004901307538</v>
+        <v>0.99698542937844492</v>
       </c>
       <c r="AB54">
-        <v>126.13243476028477</v>
+        <v>55.267128061843799</v>
       </c>
       <c r="AD54" t="s">
         <v>357</v>
@@ -13243,16 +13243,16 @@
         <v>611</v>
       </c>
       <c r="AM54" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AN54" t="s">
-        <v>698</v>
+        <v>510</v>
       </c>
       <c r="AO54">
-        <v>0.99537388871055088</v>
+        <v>0.99575042910849376</v>
       </c>
       <c r="AP54">
-        <v>84.812040306566487</v>
+        <v>77.908799677615178</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13317,16 +13317,16 @@
         <v>448</v>
       </c>
       <c r="Y55" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="Z55" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="AA55">
-        <v>0.99550817361522914</v>
+        <v>0.9934828000061533</v>
       </c>
       <c r="AB55">
-        <v>82.350150387465703</v>
+        <v>119.4819998871902</v>
       </c>
       <c r="AD55" t="s">
         <v>357</v>
@@ -13353,16 +13353,16 @@
         <v>613</v>
       </c>
       <c r="AM55" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AN55" t="s">
-        <v>700</v>
+        <v>518</v>
       </c>
       <c r="AO55">
-        <v>0.99869856811798607</v>
+        <v>0.97228963156816262</v>
       </c>
       <c r="AP55">
-        <v>23.859584503589375</v>
+        <v>508.02342125035216</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -13427,16 +13427,16 @@
         <v>450</v>
       </c>
       <c r="Y56" t="s">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="Z56" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AA56">
-        <v>0.99833662864108064</v>
+        <v>0.99321708163681277</v>
       </c>
       <c r="AB56">
-        <v>30.495141580187816</v>
+        <v>124.35350332509935</v>
       </c>
       <c r="AD56" t="s">
         <v>357</v>
@@ -13463,16 +13463,16 @@
         <v>615</v>
       </c>
       <c r="AM56" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AN56" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="AO56">
-        <v>0.99571112389324046</v>
+        <v>0.99537388871055088</v>
       </c>
       <c r="AP56">
-        <v>78.629395290591617</v>
+        <v>84.812040306566487</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -13537,16 +13537,16 @@
         <v>452</v>
       </c>
       <c r="Y57" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Z57" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AA57">
-        <v>0.99718955137263765</v>
+        <v>0.99453867174093369</v>
       </c>
       <c r="AB57">
-        <v>51.524891501643573</v>
+        <v>100.12435141621516</v>
       </c>
       <c r="AD57" t="s">
         <v>357</v>
@@ -13573,16 +13573,16 @@
         <v>617</v>
       </c>
       <c r="AM57" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="AN57" t="s">
-        <v>482</v>
+        <v>701</v>
       </c>
       <c r="AO57">
-        <v>0.99417168399542333</v>
+        <v>0.99095642121575722</v>
       </c>
       <c r="AP57">
-        <v>106.85246008390632</v>
+        <v>165.79894437778461</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -13647,16 +13647,16 @@
         <v>454</v>
       </c>
       <c r="Y58" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Z58" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="AA58">
-        <v>0.99392843937740749</v>
+        <v>0.99779322861139563</v>
       </c>
       <c r="AB58">
-        <v>111.31194474752928</v>
+        <v>40.457475457746959</v>
       </c>
       <c r="AD58" t="s">
         <v>357</v>
@@ -13683,16 +13683,16 @@
         <v>619</v>
       </c>
       <c r="AM58" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AN58" t="s">
-        <v>490</v>
+        <v>703</v>
       </c>
       <c r="AO58">
-        <v>0.99597196524055454</v>
+        <v>0.97944419839266028</v>
       </c>
       <c r="AP58">
-        <v>73.847303923166677</v>
+        <v>376.85636280122765</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -13757,16 +13757,16 @@
         <v>456</v>
       </c>
       <c r="Y59" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="Z59" t="s">
-        <v>518</v>
+        <v>482</v>
       </c>
       <c r="AA59">
-        <v>0.99249760008191157</v>
+        <v>0.99452867739052209</v>
       </c>
       <c r="AB59">
-        <v>137.54399849828698</v>
+        <v>100.30758117376212</v>
       </c>
       <c r="AD59" t="s">
         <v>357</v>
@@ -13793,16 +13793,16 @@
         <v>621</v>
       </c>
       <c r="AM59" t="s">
+        <v>704</v>
+      </c>
+      <c r="AN59" t="s">
         <v>705</v>
       </c>
-      <c r="AN59" t="s">
-        <v>514</v>
-      </c>
       <c r="AO59">
-        <v>0.99592841699385404</v>
+        <v>0.9954181092030232</v>
       </c>
       <c r="AP59">
-        <v>74.645688446009217</v>
+        <v>84.001331277908477</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -13867,16 +13867,16 @@
         <v>458</v>
       </c>
       <c r="Y60" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="Z60" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AA60">
-        <v>0.99659574043303112</v>
+        <v>0.97179899661735147</v>
       </c>
       <c r="AB60">
-        <v>62.411425394430239</v>
+        <v>517.01839534855594</v>
       </c>
       <c r="AD60" t="s">
         <v>357</v>
@@ -13906,13 +13906,13 @@
         <v>706</v>
       </c>
       <c r="AN60" t="s">
-        <v>508</v>
+        <v>707</v>
       </c>
       <c r="AO60">
-        <v>0.99603503633032486</v>
+        <v>0.99528882296736398</v>
       </c>
       <c r="AP60">
-        <v>72.691000610711512</v>
+        <v>86.371578931660309</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -13977,16 +13977,16 @@
         <v>460</v>
       </c>
       <c r="Y61" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="Z61" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AA61">
-        <v>0.99619933711347464</v>
+        <v>0.99249760008191157</v>
       </c>
       <c r="AB61">
-        <v>69.678819586298616</v>
+        <v>137.54399849828698</v>
       </c>
       <c r="AD61" t="s">
         <v>357</v>
@@ -14013,16 +14013,16 @@
         <v>625</v>
       </c>
       <c r="AM61" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AN61" t="s">
-        <v>497</v>
+        <v>709</v>
       </c>
       <c r="AO61">
-        <v>0.98797149625219505</v>
+        <v>0.99790105131742324</v>
       </c>
       <c r="AP61">
-        <v>220.5225687097583</v>
+        <v>38.480725847241352</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14087,16 +14087,16 @@
         <v>462</v>
       </c>
       <c r="Y62" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="Z62" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AA62">
-        <v>0.9936489084537441</v>
+        <v>0.99659574043303112</v>
       </c>
       <c r="AB62">
-        <v>116.43667834802481</v>
+        <v>62.411425394430239</v>
       </c>
       <c r="AD62" t="s">
         <v>357</v>
@@ -14123,16 +14123,16 @@
         <v>627</v>
       </c>
       <c r="AM62" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AN62" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AO62">
-        <v>0.99095642121575722</v>
+        <v>0.99879513173533752</v>
       </c>
       <c r="AP62">
-        <v>165.79894437778461</v>
+        <v>22.089251518811956</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14197,16 +14197,16 @@
         <v>464</v>
       </c>
       <c r="Y63" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="Z63" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AA63">
-        <v>0.99646788098520922</v>
+        <v>0.99619933711347464</v>
       </c>
       <c r="AB63">
-        <v>64.755515271164327</v>
+        <v>69.678819586298616</v>
       </c>
       <c r="AD63" t="s">
         <v>357</v>
@@ -14233,16 +14233,16 @@
         <v>629</v>
       </c>
       <c r="AM63" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AN63" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AO63">
-        <v>0.97944419839266028</v>
+        <v>0.99784614270606442</v>
       </c>
       <c r="AP63">
-        <v>376.85636280122765</v>
+        <v>39.487383722152785</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14307,16 +14307,16 @@
         <v>466</v>
       </c>
       <c r="Y64" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="Z64" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="AA64">
-        <v>0.98251354146747882</v>
+        <v>0.9936489084537441</v>
       </c>
       <c r="AB64">
-        <v>320.58507309622223</v>
+        <v>116.43667834802481</v>
       </c>
       <c r="AD64" t="s">
         <v>357</v>
@@ -14343,16 +14343,16 @@
         <v>631</v>
       </c>
       <c r="AM64" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AN64" t="s">
-        <v>713</v>
+        <v>496</v>
       </c>
       <c r="AO64">
-        <v>0.99413068845869101</v>
+        <v>0.99808758387752583</v>
       </c>
       <c r="AP64">
-        <v>107.60404492399896</v>
+        <v>35.060962245360315</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14417,16 +14417,16 @@
         <v>468</v>
       </c>
       <c r="Y65" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="Z65" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="AA65">
-        <v>0.99790048553623178</v>
+        <v>0.99646788098520922</v>
       </c>
       <c r="AB65">
-        <v>38.491098502418218</v>
+        <v>64.755515271164327</v>
       </c>
       <c r="AD65" t="s">
         <v>357</v>
@@ -14453,16 +14453,16 @@
         <v>633</v>
       </c>
       <c r="AM65" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN65" t="s">
-        <v>715</v>
+        <v>482</v>
       </c>
       <c r="AO65">
-        <v>0.99516481318893724</v>
+        <v>0.99435834940894341</v>
       </c>
       <c r="AP65">
-        <v>88.645091536150389</v>
+        <v>103.43026083603691</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -14527,16 +14527,16 @@
         <v>470</v>
       </c>
       <c r="Y66" t="s">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="Z66" t="s">
-        <v>523</v>
+        <v>483</v>
       </c>
       <c r="AA66">
-        <v>0.99660921899151722</v>
+        <v>0.98251354146747882</v>
       </c>
       <c r="AB66">
-        <v>62.164318488851343</v>
+        <v>320.58507309622223</v>
       </c>
       <c r="AD66" t="s">
         <v>357</v>
@@ -14566,13 +14566,13 @@
         <v>716</v>
       </c>
       <c r="AN66" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="AO66">
-        <v>0.99575042910849376</v>
+        <v>0.96791285861067489</v>
       </c>
       <c r="AP66">
-        <v>77.908799677615178</v>
+        <v>588.26425880429485</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -14637,16 +14637,16 @@
         <v>472</v>
       </c>
       <c r="Y67" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="Z67" t="s">
-        <v>524</v>
+        <v>485</v>
       </c>
       <c r="AA67">
-        <v>0.99069501978739871</v>
+        <v>0.99790048553623178</v>
       </c>
       <c r="AB67">
-        <v>170.59130389769052</v>
+        <v>38.491098502418218</v>
       </c>
       <c r="AD67" t="s">
         <v>357</v>
@@ -14679,10 +14679,10 @@
         <v>485</v>
       </c>
       <c r="AO67">
-        <v>0.97228963156816262</v>
+        <v>0.97537069175149649</v>
       </c>
       <c r="AP67">
-        <v>508.02342125035216</v>
+        <v>451.53731788923056</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -14747,16 +14747,16 @@
         <v>474</v>
       </c>
       <c r="Y68" t="s">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="Z68" t="s">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="AA68">
-        <v>0.98761355430624809</v>
+        <v>0.99747091457046144</v>
       </c>
       <c r="AB68">
-        <v>227.08483771878468</v>
+        <v>46.366566208207523</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -14821,16 +14821,16 @@
         <v>476</v>
       </c>
       <c r="Y69" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="Z69" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="AA69">
-        <v>0.97378904282165912</v>
+        <v>0.99505083080645407</v>
       </c>
       <c r="AB69">
-        <v>480.53421493624944</v>
+        <v>90.734768548341648</v>
       </c>
     </row>
   </sheetData>
@@ -14839,7 +14839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43FC5190-A6EB-4C57-B8C9-14D6D919A5CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC3A2E6-2C6A-464C-83DB-E4D95D7BBFCF}">
   <dimension ref="B9:Z67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -14951,7 +14951,7 @@
         <v>768</v>
       </c>
       <c r="K11" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="L11">
         <v>40.876322228443982</v>
@@ -14984,7 +14984,7 @@
         <v>882</v>
       </c>
       <c r="X11" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="Y11">
         <v>28.390499999999999</v>
@@ -15019,7 +15019,7 @@
         <v>770</v>
       </c>
       <c r="K12" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="L12">
         <v>50.805488525795006</v>
@@ -15052,7 +15052,7 @@
         <v>884</v>
       </c>
       <c r="X12" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="Y12">
         <v>11.62425</v>
@@ -15087,7 +15087,7 @@
         <v>772</v>
       </c>
       <c r="K13" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="L13">
         <v>45.019365428022141</v>
@@ -15120,7 +15120,7 @@
         <v>886</v>
       </c>
       <c r="X13" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="Y13">
         <v>21.47775</v>
@@ -15155,7 +15155,7 @@
         <v>774</v>
       </c>
       <c r="K14" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="L14">
         <v>38.91400567873454</v>
@@ -15188,7 +15188,7 @@
         <v>888</v>
       </c>
       <c r="X14" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="Y14">
         <v>0.34050000000000002</v>
@@ -15223,7 +15223,7 @@
         <v>776</v>
       </c>
       <c r="K15" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="L15">
         <v>37.911583109814686</v>
@@ -15256,7 +15256,7 @@
         <v>890</v>
       </c>
       <c r="X15" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="Y15">
         <v>4.2637499999999999</v>
@@ -15291,7 +15291,7 @@
         <v>778</v>
       </c>
       <c r="K16" t="s">
-        <v>686</v>
+        <v>655</v>
       </c>
       <c r="L16">
         <v>37.473370534574258</v>
@@ -15324,7 +15324,7 @@
         <v>892</v>
       </c>
       <c r="X16" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="Y16">
         <v>27.628499999999999</v>
@@ -15359,7 +15359,7 @@
         <v>780</v>
       </c>
       <c r="K17" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="L17">
         <v>41.688010174294369</v>
@@ -15392,7 +15392,7 @@
         <v>894</v>
       </c>
       <c r="X17" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="Y17">
         <v>27.764250000000001</v>
@@ -15427,7 +15427,7 @@
         <v>782</v>
       </c>
       <c r="K18" t="s">
-        <v>672</v>
+        <v>646</v>
       </c>
       <c r="L18">
         <v>75.015285518414572</v>
@@ -15460,7 +15460,7 @@
         <v>896</v>
       </c>
       <c r="X18" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="Y18">
         <v>31.658999999999999</v>
@@ -15495,7 +15495,7 @@
         <v>784</v>
       </c>
       <c r="K19" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="L19">
         <v>45.444678890317704</v>
@@ -15528,7 +15528,7 @@
         <v>898</v>
       </c>
       <c r="X19" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="Y19">
         <v>16.41</v>
@@ -15563,7 +15563,7 @@
         <v>786</v>
       </c>
       <c r="K20" t="s">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="L20">
         <v>56.298031950426989</v>
@@ -15596,7 +15596,7 @@
         <v>900</v>
       </c>
       <c r="X20" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="Y20">
         <v>15.04425</v>
@@ -15631,7 +15631,7 @@
         <v>788</v>
       </c>
       <c r="K21" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="L21">
         <v>40.148082022530652</v>
@@ -15664,7 +15664,7 @@
         <v>902</v>
       </c>
       <c r="X21" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="Y21">
         <v>25.41075</v>
@@ -15699,7 +15699,7 @@
         <v>790</v>
       </c>
       <c r="K22" t="s">
-        <v>670</v>
+        <v>717</v>
       </c>
       <c r="L22">
         <v>46.794583431146464</v>
@@ -15732,7 +15732,7 @@
         <v>904</v>
       </c>
       <c r="X22" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="Y22">
         <v>25.449000000000002</v>
@@ -15767,7 +15767,7 @@
         <v>792</v>
       </c>
       <c r="K23" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="L23">
         <v>43.287064660921345</v>
@@ -15800,7 +15800,7 @@
         <v>906</v>
       </c>
       <c r="X23" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="Y23">
         <v>25.623000000000001</v>
@@ -15835,7 +15835,7 @@
         <v>794</v>
       </c>
       <c r="K24" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="L24">
         <v>33.920069303175502</v>
@@ -15868,7 +15868,7 @@
         <v>908</v>
       </c>
       <c r="X24" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="Y24">
         <v>4.7872500000000002</v>
@@ -15903,7 +15903,7 @@
         <v>796</v>
       </c>
       <c r="K25" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="L25">
         <v>55.947913269125685</v>
@@ -15936,7 +15936,7 @@
         <v>910</v>
       </c>
       <c r="X25" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="Y25">
         <v>32.130749999999999</v>
@@ -15971,7 +15971,7 @@
         <v>798</v>
       </c>
       <c r="K26" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="L26">
         <v>43.00072765840126</v>
@@ -16006,7 +16006,7 @@
         <v>800</v>
       </c>
       <c r="K27" t="s">
-        <v>707</v>
+        <v>650</v>
       </c>
       <c r="L27">
         <v>39.635478438315815</v>
@@ -16041,7 +16041,7 @@
         <v>802</v>
       </c>
       <c r="K28" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="L28">
         <v>49.855646687868791</v>
@@ -16076,7 +16076,7 @@
         <v>804</v>
       </c>
       <c r="K29" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="L29">
         <v>18.30570704636682</v>
@@ -16111,7 +16111,7 @@
         <v>806</v>
       </c>
       <c r="K30" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="L30">
         <v>12.148679200397462</v>
@@ -16146,7 +16146,7 @@
         <v>808</v>
       </c>
       <c r="K31" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="L31">
         <v>26.575075296659808</v>
@@ -16181,7 +16181,7 @@
         <v>810</v>
       </c>
       <c r="K32" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L32">
         <v>38.722847502033055</v>
@@ -16216,7 +16216,7 @@
         <v>812</v>
       </c>
       <c r="K33" t="s">
-        <v>701</v>
+        <v>653</v>
       </c>
       <c r="L33">
         <v>11.567890620729482</v>
@@ -16251,7 +16251,7 @@
         <v>814</v>
       </c>
       <c r="K34" t="s">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="L34">
         <v>39.131536885301792</v>
@@ -16286,7 +16286,7 @@
         <v>816</v>
       </c>
       <c r="K35" t="s">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="L35">
         <v>20.394740302735183</v>
@@ -16321,7 +16321,7 @@
         <v>818</v>
       </c>
       <c r="K36" t="s">
-        <v>661</v>
+        <v>708</v>
       </c>
       <c r="L36">
         <v>9.0406747404738947</v>
@@ -16356,7 +16356,7 @@
         <v>820</v>
       </c>
       <c r="K37" t="s">
-        <v>699</v>
+        <v>651</v>
       </c>
       <c r="L37">
         <v>6.4322833829685422</v>
@@ -16391,7 +16391,7 @@
         <v>822</v>
       </c>
       <c r="K38" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="L38">
         <v>35.845061923353079</v>
@@ -16426,7 +16426,7 @@
         <v>824</v>
       </c>
       <c r="K39" t="s">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="L39">
         <v>14.004652736039368</v>
@@ -16461,7 +16461,7 @@
         <v>826</v>
       </c>
       <c r="K40" t="s">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="L40">
         <v>18.855237278322775</v>
@@ -16496,7 +16496,7 @@
         <v>828</v>
       </c>
       <c r="K41" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="L41">
         <v>1.5223012124511435</v>
@@ -16531,7 +16531,7 @@
         <v>830</v>
       </c>
       <c r="K42" t="s">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="L42">
         <v>8.769590617684651</v>
@@ -16566,7 +16566,7 @@
         <v>832</v>
       </c>
       <c r="K43" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="L43">
         <v>12.224014376407929</v>
@@ -16601,7 +16601,7 @@
         <v>834</v>
       </c>
       <c r="K44" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="L44">
         <v>7.8604281920366468</v>
@@ -16636,7 +16636,7 @@
         <v>836</v>
       </c>
       <c r="K45" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="L45">
         <v>57.93121461085844</v>
@@ -16671,7 +16671,7 @@
         <v>838</v>
       </c>
       <c r="K46" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="L46">
         <v>29.866420567467728</v>
@@ -16706,7 +16706,7 @@
         <v>840</v>
       </c>
       <c r="K47" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="L47">
         <v>18.251138666339184</v>
@@ -16741,7 +16741,7 @@
         <v>842</v>
       </c>
       <c r="K48" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="L48">
         <v>41.990618471497193</v>
@@ -16776,7 +16776,7 @@
         <v>844</v>
       </c>
       <c r="K49" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="L49">
         <v>47.169721640545575</v>
@@ -16811,7 +16811,7 @@
         <v>846</v>
       </c>
       <c r="K50" t="s">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="L50">
         <v>32.605660023080361</v>
@@ -16846,7 +16846,7 @@
         <v>848</v>
       </c>
       <c r="K51" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="L51">
         <v>90.299482586246782</v>
@@ -16881,7 +16881,7 @@
         <v>850</v>
       </c>
       <c r="K52" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="L52">
         <v>31.0700693659116</v>
@@ -16916,7 +16916,7 @@
         <v>852</v>
       </c>
       <c r="K53" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="L53">
         <v>50.190949831504739</v>
@@ -16951,7 +16951,7 @@
         <v>854</v>
       </c>
       <c r="K54" t="s">
-        <v>657</v>
+        <v>704</v>
       </c>
       <c r="L54">
         <v>40.782965241127428</v>
@@ -16986,7 +16986,7 @@
         <v>856</v>
       </c>
       <c r="K55" t="s">
-        <v>704</v>
+        <v>647</v>
       </c>
       <c r="L55">
         <v>18.78620106480027</v>
@@ -17021,7 +17021,7 @@
         <v>858</v>
       </c>
       <c r="K56" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="L56">
         <v>36.951713341225911</v>
@@ -17056,7 +17056,7 @@
         <v>860</v>
       </c>
       <c r="K57" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="L57">
         <v>38.681111469396185</v>
@@ -17091,7 +17091,7 @@
         <v>862</v>
       </c>
       <c r="K58" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="L58">
         <v>40.509643950316452</v>
@@ -17126,7 +17126,7 @@
         <v>864</v>
       </c>
       <c r="K59" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="L59">
         <v>51.325262704004658</v>
@@ -17161,7 +17161,7 @@
         <v>866</v>
       </c>
       <c r="K60" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="L60">
         <v>47.319604251931622</v>
@@ -17196,7 +17196,7 @@
         <v>868</v>
       </c>
       <c r="K61" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="L61">
         <v>62.987880701562105</v>
@@ -17231,7 +17231,7 @@
         <v>870</v>
       </c>
       <c r="K62" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="L62">
         <v>31.448844031219011</v>
@@ -17266,7 +17266,7 @@
         <v>872</v>
       </c>
       <c r="K63" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="L63">
         <v>42.295461693466549</v>
@@ -17301,7 +17301,7 @@
         <v>874</v>
       </c>
       <c r="K64" t="s">
-        <v>706</v>
+        <v>649</v>
       </c>
       <c r="L64">
         <v>36.453082158597873</v>
@@ -17336,7 +17336,7 @@
         <v>876</v>
       </c>
       <c r="K65" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
       <c r="L65">
         <v>35.791395793730615</v>
@@ -17371,7 +17371,7 @@
         <v>878</v>
       </c>
       <c r="K66" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="L66">
         <v>50.483450907118872</v>
@@ -17406,7 +17406,7 @@
         <v>880</v>
       </c>
       <c r="K67" t="s">
-        <v>705</v>
+        <v>648</v>
       </c>
       <c r="L67">
         <v>34.486778648232125</v>
@@ -17421,7 +17421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4307B48-093E-4BEC-928F-FF1517F10F72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705E0E48-6B44-4A61-9C77-BA3609C90FCC}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
